--- a/РАБОЧИЙ СТОЛ/расчет Останкино КИ/дв 06,07,26 млрсч ост ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет Останкино КИ/дв 06,07,26 млрсч ост ки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B19B2B0-F9CB-48EB-8853-921C17E153EA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE7A9CD-3284-491A-BF41-681CB418CD7C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AC$104</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -875,8 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AW499"/>
+  <dimension ref="A1:AU499"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -894,10 +893,10 @@
     <col min="22" max="27" width="6" customWidth="1"/>
     <col min="28" max="28" width="32.85546875" customWidth="1"/>
     <col min="29" max="29" width="7" customWidth="1"/>
-    <col min="30" max="49" width="8" customWidth="1"/>
+    <col min="30" max="47" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -945,10 +944,8 @@
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
       <c r="AU1" s="1"/>
-      <c r="AV1" s="1"/>
-      <c r="AW1" s="1"/>
-    </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -996,10 +993,8 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
       <c r="AU2" s="1"/>
-      <c r="AV2" s="1"/>
-      <c r="AW2" s="1"/>
-    </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1105,10 +1100,8 @@
       <c r="AS3" s="1"/>
       <c r="AT3" s="1"/>
       <c r="AU3" s="1"/>
-      <c r="AV3" s="1"/>
-      <c r="AW3" s="1"/>
-    </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1176,10 +1169,8 @@
       <c r="AS4" s="1"/>
       <c r="AT4" s="1"/>
       <c r="AU4" s="1"/>
-      <c r="AV4" s="1"/>
-      <c r="AW4" s="1"/>
-    </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1281,10 +1272,8 @@
       <c r="AS5" s="1"/>
       <c r="AT5" s="1"/>
       <c r="AU5" s="1"/>
-      <c r="AV5" s="1"/>
-      <c r="AW5" s="1"/>
-    </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -1388,10 +1377,8 @@
       <c r="AS6" s="1"/>
       <c r="AT6" s="1"/>
       <c r="AU6" s="1"/>
-      <c r="AV6" s="1"/>
-      <c r="AW6" s="1"/>
-    </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
@@ -1492,10 +1479,8 @@
       <c r="AS7" s="1"/>
       <c r="AT7" s="1"/>
       <c r="AU7" s="1"/>
-      <c r="AV7" s="1"/>
-      <c r="AW7" s="1"/>
-    </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -1596,10 +1581,8 @@
       <c r="AS8" s="1"/>
       <c r="AT8" s="1"/>
       <c r="AU8" s="1"/>
-      <c r="AV8" s="1"/>
-      <c r="AW8" s="1"/>
-    </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -1651,7 +1634,7 @@
         <v>35.211200000000005</v>
       </c>
       <c r="S9" s="5">
-        <f t="shared" ref="S7:S27" si="7">14*R9-Q9-P9-O9-F9</f>
+        <f t="shared" ref="S9:S26" si="7">14*R9-Q9-P9-O9-F9</f>
         <v>124.92080000000004</v>
       </c>
       <c r="T9" s="1">
@@ -1703,10 +1686,8 @@
       <c r="AS9" s="1"/>
       <c r="AT9" s="1"/>
       <c r="AU9" s="1"/>
-      <c r="AV9" s="1"/>
-      <c r="AW9" s="1"/>
-    </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -1807,10 +1788,8 @@
       <c r="AS10" s="1"/>
       <c r="AT10" s="1"/>
       <c r="AU10" s="1"/>
-      <c r="AV10" s="1"/>
-      <c r="AW10" s="1"/>
-    </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -1909,10 +1888,8 @@
       <c r="AS11" s="1"/>
       <c r="AT11" s="1"/>
       <c r="AU11" s="1"/>
-      <c r="AV11" s="1"/>
-      <c r="AW11" s="1"/>
-    </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
@@ -2011,10 +1988,8 @@
       <c r="AS12" s="1"/>
       <c r="AT12" s="1"/>
       <c r="AU12" s="1"/>
-      <c r="AV12" s="1"/>
-      <c r="AW12" s="1"/>
-    </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
@@ -2115,10 +2090,8 @@
       <c r="AS13" s="1"/>
       <c r="AT13" s="1"/>
       <c r="AU13" s="1"/>
-      <c r="AV13" s="1"/>
-      <c r="AW13" s="1"/>
-    </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
@@ -2217,10 +2190,8 @@
       <c r="AS14" s="1"/>
       <c r="AT14" s="1"/>
       <c r="AU14" s="1"/>
-      <c r="AV14" s="1"/>
-      <c r="AW14" s="1"/>
-    </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -2321,10 +2292,8 @@
       <c r="AS15" s="1"/>
       <c r="AT15" s="1"/>
       <c r="AU15" s="1"/>
-      <c r="AV15" s="1"/>
-      <c r="AW15" s="1"/>
-    </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -2425,10 +2394,8 @@
       <c r="AS16" s="1"/>
       <c r="AT16" s="1"/>
       <c r="AU16" s="1"/>
-      <c r="AV16" s="1"/>
-      <c r="AW16" s="1"/>
-    </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
@@ -2527,10 +2494,8 @@
       <c r="AS17" s="1"/>
       <c r="AT17" s="1"/>
       <c r="AU17" s="1"/>
-      <c r="AV17" s="1"/>
-      <c r="AW17" s="1"/>
-    </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
@@ -2628,10 +2593,8 @@
       <c r="AS18" s="1"/>
       <c r="AT18" s="1"/>
       <c r="AU18" s="1"/>
-      <c r="AV18" s="1"/>
-      <c r="AW18" s="1"/>
-    </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>45</v>
       </c>
@@ -2732,10 +2695,8 @@
       <c r="AS19" s="1"/>
       <c r="AT19" s="1"/>
       <c r="AU19" s="1"/>
-      <c r="AV19" s="1"/>
-      <c r="AW19" s="1"/>
-    </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>47</v>
       </c>
@@ -2836,10 +2797,8 @@
       <c r="AS20" s="1"/>
       <c r="AT20" s="1"/>
       <c r="AU20" s="1"/>
-      <c r="AV20" s="1"/>
-      <c r="AW20" s="1"/>
-    </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
@@ -2938,10 +2897,8 @@
       <c r="AS21" s="1"/>
       <c r="AT21" s="1"/>
       <c r="AU21" s="1"/>
-      <c r="AV21" s="1"/>
-      <c r="AW21" s="1"/>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
@@ -3045,10 +3002,8 @@
       <c r="AS22" s="1"/>
       <c r="AT22" s="1"/>
       <c r="AU22" s="1"/>
-      <c r="AV22" s="1"/>
-      <c r="AW22" s="1"/>
-    </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -3070,7 +3025,9 @@
       <c r="G23" s="7">
         <v>1</v>
       </c>
-      <c r="H23" s="1"/>
+      <c r="H23" s="1">
+        <v>40</v>
+      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1">
@@ -3145,10 +3102,8 @@
       <c r="AS23" s="1"/>
       <c r="AT23" s="1"/>
       <c r="AU23" s="1"/>
-      <c r="AV23" s="1"/>
-      <c r="AW23" s="1"/>
-    </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>51</v>
       </c>
@@ -3247,10 +3202,8 @@
       <c r="AS24" s="1"/>
       <c r="AT24" s="1"/>
       <c r="AU24" s="1"/>
-      <c r="AV24" s="1"/>
-      <c r="AW24" s="1"/>
-    </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>52</v>
       </c>
@@ -3352,10 +3305,8 @@
       <c r="AS25" s="1"/>
       <c r="AT25" s="1"/>
       <c r="AU25" s="1"/>
-      <c r="AV25" s="1"/>
-      <c r="AW25" s="1"/>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>53</v>
       </c>
@@ -3457,10 +3408,8 @@
       <c r="AS26" s="1"/>
       <c r="AT26" s="1"/>
       <c r="AU26" s="1"/>
-      <c r="AV26" s="1"/>
-      <c r="AW26" s="1"/>
-    </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
@@ -3561,10 +3510,8 @@
       <c r="AS27" s="1"/>
       <c r="AT27" s="1"/>
       <c r="AU27" s="1"/>
-      <c r="AV27" s="1"/>
-      <c r="AW27" s="1"/>
-    </row>
-    <row r="28" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>55</v>
       </c>
@@ -3654,10 +3601,8 @@
       <c r="AS28" s="1"/>
       <c r="AT28" s="1"/>
       <c r="AU28" s="1"/>
-      <c r="AV28" s="1"/>
-      <c r="AW28" s="1"/>
-    </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>58</v>
       </c>
@@ -3758,10 +3703,8 @@
       <c r="AS29" s="1"/>
       <c r="AT29" s="1"/>
       <c r="AU29" s="1"/>
-      <c r="AV29" s="1"/>
-      <c r="AW29" s="1"/>
-    </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -3813,7 +3756,7 @@
         <v>59.512199999999993</v>
       </c>
       <c r="S30" s="5">
-        <f t="shared" ref="S29:S65" si="9">14*R30-Q30-P30-O30-F30</f>
+        <f t="shared" ref="S30:S65" si="9">14*R30-Q30-P30-O30-F30</f>
         <v>196.93179999999987</v>
       </c>
       <c r="T30" s="1">
@@ -3865,10 +3808,8 @@
       <c r="AS30" s="1"/>
       <c r="AT30" s="1"/>
       <c r="AU30" s="1"/>
-      <c r="AV30" s="1"/>
-      <c r="AW30" s="1"/>
-    </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
@@ -3967,10 +3908,8 @@
       <c r="AS31" s="1"/>
       <c r="AT31" s="1"/>
       <c r="AU31" s="1"/>
-      <c r="AV31" s="1"/>
-      <c r="AW31" s="1"/>
-    </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>61</v>
       </c>
@@ -4074,10 +4013,8 @@
       <c r="AS32" s="1"/>
       <c r="AT32" s="1"/>
       <c r="AU32" s="1"/>
-      <c r="AV32" s="1"/>
-      <c r="AW32" s="1"/>
-    </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>62</v>
       </c>
@@ -4181,10 +4118,8 @@
       <c r="AS33" s="1"/>
       <c r="AT33" s="1"/>
       <c r="AU33" s="1"/>
-      <c r="AV33" s="1"/>
-      <c r="AW33" s="1"/>
-    </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>63</v>
       </c>
@@ -4288,10 +4223,8 @@
       <c r="AS34" s="1"/>
       <c r="AT34" s="1"/>
       <c r="AU34" s="1"/>
-      <c r="AV34" s="1"/>
-      <c r="AW34" s="1"/>
-    </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>64</v>
       </c>
@@ -4392,10 +4325,8 @@
       <c r="AS35" s="1"/>
       <c r="AT35" s="1"/>
       <c r="AU35" s="1"/>
-      <c r="AV35" s="1"/>
-      <c r="AW35" s="1"/>
-    </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>65</v>
       </c>
@@ -4496,10 +4427,8 @@
       <c r="AS36" s="1"/>
       <c r="AT36" s="1"/>
       <c r="AU36" s="1"/>
-      <c r="AV36" s="1"/>
-      <c r="AW36" s="1"/>
-    </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>66</v>
       </c>
@@ -4601,10 +4530,8 @@
       <c r="AS37" s="1"/>
       <c r="AT37" s="1"/>
       <c r="AU37" s="1"/>
-      <c r="AV37" s="1"/>
-      <c r="AW37" s="1"/>
-    </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>67</v>
       </c>
@@ -4624,7 +4551,9 @@
       <c r="G38" s="7">
         <v>1</v>
       </c>
-      <c r="H38" s="1"/>
+      <c r="H38" s="1">
+        <v>45</v>
+      </c>
       <c r="I38" s="1">
         <v>6470</v>
       </c>
@@ -4699,10 +4628,8 @@
       <c r="AS38" s="1"/>
       <c r="AT38" s="1"/>
       <c r="AU38" s="1"/>
-      <c r="AV38" s="1"/>
-      <c r="AW38" s="1"/>
-    </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>69</v>
       </c>
@@ -4803,10 +4730,8 @@
       <c r="AS39" s="1"/>
       <c r="AT39" s="1"/>
       <c r="AU39" s="1"/>
-      <c r="AV39" s="1"/>
-      <c r="AW39" s="1"/>
-    </row>
-    <row r="40" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>70</v>
       </c>
@@ -4828,7 +4753,9 @@
       <c r="G40" s="7">
         <v>0.3</v>
       </c>
-      <c r="H40" s="1"/>
+      <c r="H40" s="1">
+        <v>45</v>
+      </c>
       <c r="I40" s="1">
         <v>6495</v>
       </c>
@@ -4905,10 +4832,8 @@
       <c r="AS40" s="1"/>
       <c r="AT40" s="1"/>
       <c r="AU40" s="1"/>
-      <c r="AV40" s="1"/>
-      <c r="AW40" s="1"/>
-    </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>71</v>
       </c>
@@ -5009,10 +4934,8 @@
       <c r="AS41" s="1"/>
       <c r="AT41" s="1"/>
       <c r="AU41" s="1"/>
-      <c r="AV41" s="1"/>
-      <c r="AW41" s="1"/>
-    </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>72</v>
       </c>
@@ -5113,10 +5036,8 @@
       <c r="AS42" s="1"/>
       <c r="AT42" s="1"/>
       <c r="AU42" s="1"/>
-      <c r="AV42" s="1"/>
-      <c r="AW42" s="1"/>
-    </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>73</v>
       </c>
@@ -5217,10 +5138,8 @@
       <c r="AS43" s="1"/>
       <c r="AT43" s="1"/>
       <c r="AU43" s="1"/>
-      <c r="AV43" s="1"/>
-      <c r="AW43" s="1"/>
-    </row>
-    <row r="44" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>74</v>
       </c>
@@ -5321,10 +5240,8 @@
       <c r="AS44" s="1"/>
       <c r="AT44" s="1"/>
       <c r="AU44" s="1"/>
-      <c r="AV44" s="1"/>
-      <c r="AW44" s="1"/>
-    </row>
-    <row r="45" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>75</v>
       </c>
@@ -5426,10 +5343,8 @@
       <c r="AS45" s="1"/>
       <c r="AT45" s="1"/>
       <c r="AU45" s="1"/>
-      <c r="AV45" s="1"/>
-      <c r="AW45" s="1"/>
-    </row>
-    <row r="46" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>76</v>
       </c>
@@ -5528,10 +5443,8 @@
       <c r="AS46" s="1"/>
       <c r="AT46" s="1"/>
       <c r="AU46" s="1"/>
-      <c r="AV46" s="1"/>
-      <c r="AW46" s="1"/>
-    </row>
-    <row r="47" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>77</v>
       </c>
@@ -5630,10 +5543,8 @@
       <c r="AS47" s="1"/>
       <c r="AT47" s="1"/>
       <c r="AU47" s="1"/>
-      <c r="AV47" s="1"/>
-      <c r="AW47" s="1"/>
-    </row>
-    <row r="48" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>78</v>
       </c>
@@ -5734,10 +5645,8 @@
       <c r="AS48" s="1"/>
       <c r="AT48" s="1"/>
       <c r="AU48" s="1"/>
-      <c r="AV48" s="1"/>
-      <c r="AW48" s="1"/>
-    </row>
-    <row r="49" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>79</v>
       </c>
@@ -5841,10 +5750,8 @@
       <c r="AS49" s="1"/>
       <c r="AT49" s="1"/>
       <c r="AU49" s="1"/>
-      <c r="AV49" s="1"/>
-      <c r="AW49" s="1"/>
-    </row>
-    <row r="50" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>80</v>
       </c>
@@ -5948,10 +5855,8 @@
       <c r="AS50" s="1"/>
       <c r="AT50" s="1"/>
       <c r="AU50" s="1"/>
-      <c r="AV50" s="1"/>
-      <c r="AW50" s="1"/>
-    </row>
-    <row r="51" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>81</v>
       </c>
@@ -6055,10 +5960,8 @@
       <c r="AS51" s="1"/>
       <c r="AT51" s="1"/>
       <c r="AU51" s="1"/>
-      <c r="AV51" s="1"/>
-      <c r="AW51" s="1"/>
-    </row>
-    <row r="52" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>82</v>
       </c>
@@ -6159,10 +6062,8 @@
       <c r="AS52" s="1"/>
       <c r="AT52" s="1"/>
       <c r="AU52" s="1"/>
-      <c r="AV52" s="1"/>
-      <c r="AW52" s="1"/>
-    </row>
-    <row r="53" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>83</v>
       </c>
@@ -6261,10 +6162,8 @@
       <c r="AS53" s="1"/>
       <c r="AT53" s="1"/>
       <c r="AU53" s="1"/>
-      <c r="AV53" s="1"/>
-      <c r="AW53" s="1"/>
-    </row>
-    <row r="54" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>84</v>
       </c>
@@ -6286,7 +6185,9 @@
       <c r="G54" s="7">
         <v>0.4</v>
       </c>
-      <c r="H54" s="1"/>
+      <c r="H54" s="1">
+        <v>60</v>
+      </c>
       <c r="I54" s="1">
         <v>6797</v>
       </c>
@@ -6361,10 +6262,8 @@
       <c r="AS54" s="1"/>
       <c r="AT54" s="1"/>
       <c r="AU54" s="1"/>
-      <c r="AV54" s="1"/>
-      <c r="AW54" s="1"/>
-    </row>
-    <row r="55" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>85</v>
       </c>
@@ -6465,10 +6364,8 @@
       <c r="AS55" s="1"/>
       <c r="AT55" s="1"/>
       <c r="AU55" s="1"/>
-      <c r="AV55" s="1"/>
-      <c r="AW55" s="1"/>
-    </row>
-    <row r="56" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>86</v>
       </c>
@@ -6572,10 +6469,8 @@
       <c r="AS56" s="1"/>
       <c r="AT56" s="1"/>
       <c r="AU56" s="1"/>
-      <c r="AV56" s="1"/>
-      <c r="AW56" s="1"/>
-    </row>
-    <row r="57" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>87</v>
       </c>
@@ -6668,10 +6563,8 @@
       <c r="AS57" s="1"/>
       <c r="AT57" s="1"/>
       <c r="AU57" s="1"/>
-      <c r="AV57" s="1"/>
-      <c r="AW57" s="1"/>
-    </row>
-    <row r="58" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>88</v>
       </c>
@@ -6773,10 +6666,8 @@
       <c r="AS58" s="1"/>
       <c r="AT58" s="1"/>
       <c r="AU58" s="1"/>
-      <c r="AV58" s="1"/>
-      <c r="AW58" s="1"/>
-    </row>
-    <row r="59" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>89</v>
       </c>
@@ -6798,7 +6689,9 @@
       <c r="G59" s="7">
         <v>1</v>
       </c>
-      <c r="H59" s="1"/>
+      <c r="H59" s="1">
+        <v>60</v>
+      </c>
       <c r="I59" s="1">
         <v>6861</v>
       </c>
@@ -6875,10 +6768,8 @@
       <c r="AS59" s="1"/>
       <c r="AT59" s="1"/>
       <c r="AU59" s="1"/>
-      <c r="AV59" s="1"/>
-      <c r="AW59" s="1"/>
-    </row>
-    <row r="60" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>90</v>
       </c>
@@ -6896,7 +6787,9 @@
       <c r="G60" s="7">
         <v>1</v>
       </c>
-      <c r="H60" s="1"/>
+      <c r="H60" s="1">
+        <v>60</v>
+      </c>
       <c r="I60" s="1">
         <v>6892</v>
       </c>
@@ -6971,10 +6864,8 @@
       <c r="AS60" s="1"/>
       <c r="AT60" s="1"/>
       <c r="AU60" s="1"/>
-      <c r="AV60" s="1"/>
-      <c r="AW60" s="1"/>
-    </row>
-    <row r="61" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>91</v>
       </c>
@@ -7075,10 +6966,8 @@
       <c r="AS61" s="1"/>
       <c r="AT61" s="1"/>
       <c r="AU61" s="1"/>
-      <c r="AV61" s="1"/>
-      <c r="AW61" s="1"/>
-    </row>
-    <row r="62" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>92</v>
       </c>
@@ -7180,10 +7069,8 @@
       <c r="AS62" s="1"/>
       <c r="AT62" s="1"/>
       <c r="AU62" s="1"/>
-      <c r="AV62" s="1"/>
-      <c r="AW62" s="1"/>
-    </row>
-    <row r="63" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>93</v>
       </c>
@@ -7285,10 +7172,8 @@
       <c r="AS63" s="1"/>
       <c r="AT63" s="1"/>
       <c r="AU63" s="1"/>
-      <c r="AV63" s="1"/>
-      <c r="AW63" s="1"/>
-    </row>
-    <row r="64" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>94</v>
       </c>
@@ -7310,7 +7195,9 @@
       <c r="G64" s="7">
         <v>0.3</v>
       </c>
-      <c r="H64" s="1"/>
+      <c r="H64" s="1">
+        <v>60</v>
+      </c>
       <c r="I64" s="1">
         <v>7059</v>
       </c>
@@ -7389,10 +7276,8 @@
       <c r="AS64" s="1"/>
       <c r="AT64" s="1"/>
       <c r="AU64" s="1"/>
-      <c r="AV64" s="1"/>
-      <c r="AW64" s="1"/>
-    </row>
-    <row r="65" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>95</v>
       </c>
@@ -7498,10 +7383,8 @@
       <c r="AS65" s="1"/>
       <c r="AT65" s="1"/>
       <c r="AU65" s="1"/>
-      <c r="AV65" s="1"/>
-      <c r="AW65" s="1"/>
-    </row>
-    <row r="66" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
         <v>96</v>
       </c>
@@ -7595,10 +7478,8 @@
       <c r="AS66" s="1"/>
       <c r="AT66" s="1"/>
       <c r="AU66" s="1"/>
-      <c r="AV66" s="1"/>
-      <c r="AW66" s="1"/>
-    </row>
-    <row r="67" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>97</v>
       </c>
@@ -7700,10 +7581,8 @@
       <c r="AS67" s="1"/>
       <c r="AT67" s="1"/>
       <c r="AU67" s="1"/>
-      <c r="AV67" s="1"/>
-      <c r="AW67" s="1"/>
-    </row>
-    <row r="68" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>98</v>
       </c>
@@ -7753,7 +7632,7 @@
         <v>23.2</v>
       </c>
       <c r="S68" s="5">
-        <f t="shared" ref="S67:S102" si="15">14*R68-Q68-P68-O68-F68</f>
+        <f t="shared" ref="S68:S97" si="15">14*R68-Q68-P68-O68-F68</f>
         <v>99.800000000000011</v>
       </c>
       <c r="T68" s="1">
@@ -7805,10 +7684,8 @@
       <c r="AS68" s="1"/>
       <c r="AT68" s="1"/>
       <c r="AU68" s="1"/>
-      <c r="AV68" s="1"/>
-      <c r="AW68" s="1"/>
-    </row>
-    <row r="69" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>99</v>
       </c>
@@ -7907,10 +7784,8 @@
       <c r="AS69" s="1"/>
       <c r="AT69" s="1"/>
       <c r="AU69" s="1"/>
-      <c r="AV69" s="1"/>
-      <c r="AW69" s="1"/>
-    </row>
-    <row r="70" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>100</v>
       </c>
@@ -8011,10 +7886,8 @@
       <c r="AS70" s="1"/>
       <c r="AT70" s="1"/>
       <c r="AU70" s="1"/>
-      <c r="AV70" s="1"/>
-      <c r="AW70" s="1"/>
-    </row>
-    <row r="71" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>101</v>
       </c>
@@ -8036,7 +7909,9 @@
       <c r="G71" s="7">
         <v>1</v>
       </c>
-      <c r="H71" s="1"/>
+      <c r="H71" s="1">
+        <v>50</v>
+      </c>
       <c r="I71" s="1">
         <v>7083</v>
       </c>
@@ -8116,10 +7991,8 @@
       <c r="AS71" s="1"/>
       <c r="AT71" s="1"/>
       <c r="AU71" s="1"/>
-      <c r="AV71" s="1"/>
-      <c r="AW71" s="1"/>
-    </row>
-    <row r="72" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>102</v>
       </c>
@@ -8218,10 +8091,8 @@
       <c r="AS72" s="1"/>
       <c r="AT72" s="1"/>
       <c r="AU72" s="1"/>
-      <c r="AV72" s="1"/>
-      <c r="AW72" s="1"/>
-    </row>
-    <row r="73" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>103</v>
       </c>
@@ -8241,7 +8112,9 @@
       <c r="G73" s="7">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H73" s="1"/>
+      <c r="H73" s="1">
+        <v>50</v>
+      </c>
       <c r="I73" s="1">
         <v>7092</v>
       </c>
@@ -8318,10 +8191,8 @@
       <c r="AS73" s="1"/>
       <c r="AT73" s="1"/>
       <c r="AU73" s="1"/>
-      <c r="AV73" s="1"/>
-      <c r="AW73" s="1"/>
-    </row>
-    <row r="74" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>104</v>
       </c>
@@ -8425,10 +8296,8 @@
       <c r="AS74" s="1"/>
       <c r="AT74" s="1"/>
       <c r="AU74" s="1"/>
-      <c r="AV74" s="1"/>
-      <c r="AW74" s="1"/>
-    </row>
-    <row r="75" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>105</v>
       </c>
@@ -8523,10 +8392,8 @@
       <c r="AS75" s="1"/>
       <c r="AT75" s="1"/>
       <c r="AU75" s="1"/>
-      <c r="AV75" s="1"/>
-      <c r="AW75" s="1"/>
-    </row>
-    <row r="76" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>106</v>
       </c>
@@ -8628,10 +8495,8 @@
       <c r="AS76" s="1"/>
       <c r="AT76" s="1"/>
       <c r="AU76" s="1"/>
-      <c r="AV76" s="1"/>
-      <c r="AW76" s="1"/>
-    </row>
-    <row r="77" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>107</v>
       </c>
@@ -8728,10 +8593,8 @@
       <c r="AS77" s="1"/>
       <c r="AT77" s="1"/>
       <c r="AU77" s="1"/>
-      <c r="AV77" s="1"/>
-      <c r="AW77" s="1"/>
-    </row>
-    <row r="78" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>108</v>
       </c>
@@ -8835,10 +8698,8 @@
       <c r="AS78" s="1"/>
       <c r="AT78" s="1"/>
       <c r="AU78" s="1"/>
-      <c r="AV78" s="1"/>
-      <c r="AW78" s="1"/>
-    </row>
-    <row r="79" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>109</v>
       </c>
@@ -8939,10 +8800,8 @@
       <c r="AS79" s="1"/>
       <c r="AT79" s="1"/>
       <c r="AU79" s="1"/>
-      <c r="AV79" s="1"/>
-      <c r="AW79" s="1"/>
-    </row>
-    <row r="80" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>110</v>
       </c>
@@ -9046,10 +8905,8 @@
       <c r="AS80" s="1"/>
       <c r="AT80" s="1"/>
       <c r="AU80" s="1"/>
-      <c r="AV80" s="1"/>
-      <c r="AW80" s="1"/>
-    </row>
-    <row r="81" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>111</v>
       </c>
@@ -9153,10 +9010,8 @@
       <c r="AS81" s="1"/>
       <c r="AT81" s="1"/>
       <c r="AU81" s="1"/>
-      <c r="AV81" s="1"/>
-      <c r="AW81" s="1"/>
-    </row>
-    <row r="82" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>112</v>
       </c>
@@ -9258,10 +9113,8 @@
       <c r="AS82" s="1"/>
       <c r="AT82" s="1"/>
       <c r="AU82" s="1"/>
-      <c r="AV82" s="1"/>
-      <c r="AW82" s="1"/>
-    </row>
-    <row r="83" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>113</v>
       </c>
@@ -9362,10 +9215,8 @@
       <c r="AS83" s="1"/>
       <c r="AT83" s="1"/>
       <c r="AU83" s="1"/>
-      <c r="AV83" s="1"/>
-      <c r="AW83" s="1"/>
-    </row>
-    <row r="84" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>114</v>
       </c>
@@ -9469,10 +9320,8 @@
       <c r="AS84" s="1"/>
       <c r="AT84" s="1"/>
       <c r="AU84" s="1"/>
-      <c r="AV84" s="1"/>
-      <c r="AW84" s="1"/>
-    </row>
-    <row r="85" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>115</v>
       </c>
@@ -9573,10 +9422,8 @@
       <c r="AS85" s="1"/>
       <c r="AT85" s="1"/>
       <c r="AU85" s="1"/>
-      <c r="AV85" s="1"/>
-      <c r="AW85" s="1"/>
-    </row>
-    <row r="86" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>116</v>
       </c>
@@ -9677,10 +9524,8 @@
       <c r="AS86" s="1"/>
       <c r="AT86" s="1"/>
       <c r="AU86" s="1"/>
-      <c r="AV86" s="1"/>
-      <c r="AW86" s="1"/>
-    </row>
-    <row r="87" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>117</v>
       </c>
@@ -9781,10 +9626,8 @@
       <c r="AS87" s="1"/>
       <c r="AT87" s="1"/>
       <c r="AU87" s="1"/>
-      <c r="AV87" s="1"/>
-      <c r="AW87" s="1"/>
-    </row>
-    <row r="88" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>118</v>
       </c>
@@ -9885,10 +9728,8 @@
       <c r="AS88" s="1"/>
       <c r="AT88" s="1"/>
       <c r="AU88" s="1"/>
-      <c r="AV88" s="1"/>
-      <c r="AW88" s="1"/>
-    </row>
-    <row r="89" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>119</v>
       </c>
@@ -9910,7 +9751,9 @@
       <c r="G89" s="7">
         <v>1</v>
       </c>
-      <c r="H89" s="1"/>
+      <c r="H89" s="1">
+        <v>50</v>
+      </c>
       <c r="I89" s="1">
         <v>7271</v>
       </c>
@@ -9985,10 +9828,8 @@
       <c r="AS89" s="1"/>
       <c r="AT89" s="1"/>
       <c r="AU89" s="1"/>
-      <c r="AV89" s="1"/>
-      <c r="AW89" s="1"/>
-    </row>
-    <row r="90" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>120</v>
       </c>
@@ -10010,7 +9851,9 @@
       <c r="G90" s="7">
         <v>0.3</v>
       </c>
-      <c r="H90" s="1"/>
+      <c r="H90" s="1">
+        <v>50</v>
+      </c>
       <c r="I90" s="1">
         <v>7276</v>
       </c>
@@ -10085,10 +9928,8 @@
       <c r="AS90" s="1"/>
       <c r="AT90" s="1"/>
       <c r="AU90" s="1"/>
-      <c r="AV90" s="1"/>
-      <c r="AW90" s="1"/>
-    </row>
-    <row r="91" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>121</v>
       </c>
@@ -10187,10 +10028,8 @@
       <c r="AS91" s="1"/>
       <c r="AT91" s="1"/>
       <c r="AU91" s="1"/>
-      <c r="AV91" s="1"/>
-      <c r="AW91" s="1"/>
-    </row>
-    <row r="92" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>122</v>
       </c>
@@ -10292,10 +10131,8 @@
       <c r="AS92" s="1"/>
       <c r="AT92" s="1"/>
       <c r="AU92" s="1"/>
-      <c r="AV92" s="1"/>
-      <c r="AW92" s="1"/>
-    </row>
-    <row r="93" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>123</v>
       </c>
@@ -10396,10 +10233,8 @@
       <c r="AS93" s="1"/>
       <c r="AT93" s="1"/>
       <c r="AU93" s="1"/>
-      <c r="AV93" s="1"/>
-      <c r="AW93" s="1"/>
-    </row>
-    <row r="94" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>124</v>
       </c>
@@ -10421,7 +10256,9 @@
       <c r="G94" s="7">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H94" s="1"/>
+      <c r="H94" s="1">
+        <v>50</v>
+      </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1">
@@ -10495,10 +10332,8 @@
       <c r="AS94" s="1"/>
       <c r="AT94" s="1"/>
       <c r="AU94" s="1"/>
-      <c r="AV94" s="1"/>
-      <c r="AW94" s="1"/>
-    </row>
-    <row r="95" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>125</v>
       </c>
@@ -10520,7 +10355,9 @@
       <c r="G95" s="7">
         <v>0.4</v>
       </c>
-      <c r="H95" s="1"/>
+      <c r="H95" s="1">
+        <v>60</v>
+      </c>
       <c r="I95" s="1">
         <v>7343</v>
       </c>
@@ -10598,10 +10435,8 @@
       <c r="AS95" s="1"/>
       <c r="AT95" s="1"/>
       <c r="AU95" s="1"/>
-      <c r="AV95" s="1"/>
-      <c r="AW95" s="1"/>
-    </row>
-    <row r="96" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>126</v>
       </c>
@@ -10621,7 +10456,9 @@
       <c r="G96" s="7">
         <v>0.3</v>
       </c>
-      <c r="H96" s="1"/>
+      <c r="H96" s="1">
+        <v>45</v>
+      </c>
       <c r="I96" s="1">
         <v>7371</v>
       </c>
@@ -10698,10 +10535,8 @@
       <c r="AS96" s="1"/>
       <c r="AT96" s="1"/>
       <c r="AU96" s="1"/>
-      <c r="AV96" s="1"/>
-      <c r="AW96" s="1"/>
-    </row>
-    <row r="97" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>128</v>
       </c>
@@ -10805,10 +10640,8 @@
       <c r="AS97" s="1"/>
       <c r="AT97" s="1"/>
       <c r="AU97" s="1"/>
-      <c r="AV97" s="1"/>
-      <c r="AW97" s="1"/>
-    </row>
-    <row r="98" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>129</v>
       </c>
@@ -10830,7 +10663,9 @@
       <c r="G98" s="7">
         <v>0.12</v>
       </c>
-      <c r="H98" s="1"/>
+      <c r="H98" s="1">
+        <v>30</v>
+      </c>
       <c r="I98" s="1">
         <v>7461</v>
       </c>
@@ -10905,10 +10740,8 @@
       <c r="AS98" s="1"/>
       <c r="AT98" s="1"/>
       <c r="AU98" s="1"/>
-      <c r="AV98" s="1"/>
-      <c r="AW98" s="1"/>
-    </row>
-    <row r="99" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>130</v>
       </c>
@@ -10930,7 +10763,9 @@
       <c r="G99" s="7">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H99" s="1"/>
+      <c r="H99" s="1">
+        <v>45</v>
+      </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1">
@@ -11003,10 +10838,8 @@
       <c r="AS99" s="1"/>
       <c r="AT99" s="1"/>
       <c r="AU99" s="1"/>
-      <c r="AV99" s="1"/>
-      <c r="AW99" s="1"/>
-    </row>
-    <row r="100" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>57</v>
       </c>
@@ -11024,7 +10857,9 @@
       <c r="G100" s="7">
         <v>0.4</v>
       </c>
-      <c r="H100" s="1"/>
+      <c r="H100" s="1">
+        <v>60</v>
+      </c>
       <c r="I100" s="1">
         <v>7523</v>
       </c>
@@ -11099,10 +10934,8 @@
       <c r="AS100" s="1"/>
       <c r="AT100" s="1"/>
       <c r="AU100" s="1"/>
-      <c r="AV100" s="1"/>
-      <c r="AW100" s="1"/>
-    </row>
-    <row r="101" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>131</v>
       </c>
@@ -11124,7 +10957,9 @@
       <c r="G101" s="7">
         <v>0.35</v>
       </c>
-      <c r="H101" s="1"/>
+      <c r="H101" s="1">
+        <v>60</v>
+      </c>
       <c r="I101" s="1">
         <v>7539</v>
       </c>
@@ -11199,10 +11034,8 @@
       <c r="AS101" s="1"/>
       <c r="AT101" s="1"/>
       <c r="AU101" s="1"/>
-      <c r="AV101" s="1"/>
-      <c r="AW101" s="1"/>
-    </row>
-    <row r="102" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>132</v>
       </c>
@@ -11224,7 +11057,9 @@
       <c r="G102" s="7">
         <v>0.33</v>
       </c>
-      <c r="H102" s="1"/>
+      <c r="H102" s="1">
+        <v>45</v>
+      </c>
       <c r="I102" s="1">
         <v>7603</v>
       </c>
@@ -11301,10 +11136,8 @@
       <c r="AS102" s="1"/>
       <c r="AT102" s="1"/>
       <c r="AU102" s="1"/>
-      <c r="AV102" s="1"/>
-      <c r="AW102" s="1"/>
-    </row>
-    <row r="103" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
         <v>133</v>
       </c>
@@ -11396,10 +11229,8 @@
       <c r="AS103" s="1"/>
       <c r="AT103" s="1"/>
       <c r="AU103" s="1"/>
-      <c r="AV103" s="1"/>
-      <c r="AW103" s="1"/>
-    </row>
-    <row r="104" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
         <v>135</v>
       </c>
@@ -11493,10 +11324,8 @@
       <c r="AS104" s="1"/>
       <c r="AT104" s="1"/>
       <c r="AU104" s="1"/>
-      <c r="AV104" s="1"/>
-      <c r="AW104" s="1"/>
-    </row>
-    <row r="105" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -11544,10 +11373,8 @@
       <c r="AS105" s="1"/>
       <c r="AT105" s="1"/>
       <c r="AU105" s="1"/>
-      <c r="AV105" s="1"/>
-      <c r="AW105" s="1"/>
-    </row>
-    <row r="106" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -11595,10 +11422,8 @@
       <c r="AS106" s="1"/>
       <c r="AT106" s="1"/>
       <c r="AU106" s="1"/>
-      <c r="AV106" s="1"/>
-      <c r="AW106" s="1"/>
-    </row>
-    <row r="107" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -11646,10 +11471,8 @@
       <c r="AS107" s="1"/>
       <c r="AT107" s="1"/>
       <c r="AU107" s="1"/>
-      <c r="AV107" s="1"/>
-      <c r="AW107" s="1"/>
-    </row>
-    <row r="108" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -11697,10 +11520,8 @@
       <c r="AS108" s="1"/>
       <c r="AT108" s="1"/>
       <c r="AU108" s="1"/>
-      <c r="AV108" s="1"/>
-      <c r="AW108" s="1"/>
-    </row>
-    <row r="109" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -11748,10 +11569,8 @@
       <c r="AS109" s="1"/>
       <c r="AT109" s="1"/>
       <c r="AU109" s="1"/>
-      <c r="AV109" s="1"/>
-      <c r="AW109" s="1"/>
-    </row>
-    <row r="110" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -11799,10 +11618,8 @@
       <c r="AS110" s="1"/>
       <c r="AT110" s="1"/>
       <c r="AU110" s="1"/>
-      <c r="AV110" s="1"/>
-      <c r="AW110" s="1"/>
-    </row>
-    <row r="111" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -11850,10 +11667,8 @@
       <c r="AS111" s="1"/>
       <c r="AT111" s="1"/>
       <c r="AU111" s="1"/>
-      <c r="AV111" s="1"/>
-      <c r="AW111" s="1"/>
-    </row>
-    <row r="112" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -11901,10 +11716,8 @@
       <c r="AS112" s="1"/>
       <c r="AT112" s="1"/>
       <c r="AU112" s="1"/>
-      <c r="AV112" s="1"/>
-      <c r="AW112" s="1"/>
-    </row>
-    <row r="113" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -11952,10 +11765,8 @@
       <c r="AS113" s="1"/>
       <c r="AT113" s="1"/>
       <c r="AU113" s="1"/>
-      <c r="AV113" s="1"/>
-      <c r="AW113" s="1"/>
-    </row>
-    <row r="114" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -12003,10 +11814,8 @@
       <c r="AS114" s="1"/>
       <c r="AT114" s="1"/>
       <c r="AU114" s="1"/>
-      <c r="AV114" s="1"/>
-      <c r="AW114" s="1"/>
-    </row>
-    <row r="115" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -12054,10 +11863,8 @@
       <c r="AS115" s="1"/>
       <c r="AT115" s="1"/>
       <c r="AU115" s="1"/>
-      <c r="AV115" s="1"/>
-      <c r="AW115" s="1"/>
-    </row>
-    <row r="116" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -12105,10 +11912,8 @@
       <c r="AS116" s="1"/>
       <c r="AT116" s="1"/>
       <c r="AU116" s="1"/>
-      <c r="AV116" s="1"/>
-      <c r="AW116" s="1"/>
-    </row>
-    <row r="117" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -12156,10 +11961,8 @@
       <c r="AS117" s="1"/>
       <c r="AT117" s="1"/>
       <c r="AU117" s="1"/>
-      <c r="AV117" s="1"/>
-      <c r="AW117" s="1"/>
-    </row>
-    <row r="118" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -12207,10 +12010,8 @@
       <c r="AS118" s="1"/>
       <c r="AT118" s="1"/>
       <c r="AU118" s="1"/>
-      <c r="AV118" s="1"/>
-      <c r="AW118" s="1"/>
-    </row>
-    <row r="119" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -12258,10 +12059,8 @@
       <c r="AS119" s="1"/>
       <c r="AT119" s="1"/>
       <c r="AU119" s="1"/>
-      <c r="AV119" s="1"/>
-      <c r="AW119" s="1"/>
-    </row>
-    <row r="120" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -12309,10 +12108,8 @@
       <c r="AS120" s="1"/>
       <c r="AT120" s="1"/>
       <c r="AU120" s="1"/>
-      <c r="AV120" s="1"/>
-      <c r="AW120" s="1"/>
-    </row>
-    <row r="121" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -12360,10 +12157,8 @@
       <c r="AS121" s="1"/>
       <c r="AT121" s="1"/>
       <c r="AU121" s="1"/>
-      <c r="AV121" s="1"/>
-      <c r="AW121" s="1"/>
-    </row>
-    <row r="122" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -12411,10 +12206,8 @@
       <c r="AS122" s="1"/>
       <c r="AT122" s="1"/>
       <c r="AU122" s="1"/>
-      <c r="AV122" s="1"/>
-      <c r="AW122" s="1"/>
-    </row>
-    <row r="123" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -12462,10 +12255,8 @@
       <c r="AS123" s="1"/>
       <c r="AT123" s="1"/>
       <c r="AU123" s="1"/>
-      <c r="AV123" s="1"/>
-      <c r="AW123" s="1"/>
-    </row>
-    <row r="124" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -12513,10 +12304,8 @@
       <c r="AS124" s="1"/>
       <c r="AT124" s="1"/>
       <c r="AU124" s="1"/>
-      <c r="AV124" s="1"/>
-      <c r="AW124" s="1"/>
-    </row>
-    <row r="125" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -12564,10 +12353,8 @@
       <c r="AS125" s="1"/>
       <c r="AT125" s="1"/>
       <c r="AU125" s="1"/>
-      <c r="AV125" s="1"/>
-      <c r="AW125" s="1"/>
-    </row>
-    <row r="126" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -12615,10 +12402,8 @@
       <c r="AS126" s="1"/>
       <c r="AT126" s="1"/>
       <c r="AU126" s="1"/>
-      <c r="AV126" s="1"/>
-      <c r="AW126" s="1"/>
-    </row>
-    <row r="127" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -12666,10 +12451,8 @@
       <c r="AS127" s="1"/>
       <c r="AT127" s="1"/>
       <c r="AU127" s="1"/>
-      <c r="AV127" s="1"/>
-      <c r="AW127" s="1"/>
-    </row>
-    <row r="128" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -12717,10 +12500,8 @@
       <c r="AS128" s="1"/>
       <c r="AT128" s="1"/>
       <c r="AU128" s="1"/>
-      <c r="AV128" s="1"/>
-      <c r="AW128" s="1"/>
-    </row>
-    <row r="129" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -12768,10 +12549,8 @@
       <c r="AS129" s="1"/>
       <c r="AT129" s="1"/>
       <c r="AU129" s="1"/>
-      <c r="AV129" s="1"/>
-      <c r="AW129" s="1"/>
-    </row>
-    <row r="130" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -12819,10 +12598,8 @@
       <c r="AS130" s="1"/>
       <c r="AT130" s="1"/>
       <c r="AU130" s="1"/>
-      <c r="AV130" s="1"/>
-      <c r="AW130" s="1"/>
-    </row>
-    <row r="131" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -12870,10 +12647,8 @@
       <c r="AS131" s="1"/>
       <c r="AT131" s="1"/>
       <c r="AU131" s="1"/>
-      <c r="AV131" s="1"/>
-      <c r="AW131" s="1"/>
-    </row>
-    <row r="132" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -12921,10 +12696,8 @@
       <c r="AS132" s="1"/>
       <c r="AT132" s="1"/>
       <c r="AU132" s="1"/>
-      <c r="AV132" s="1"/>
-      <c r="AW132" s="1"/>
-    </row>
-    <row r="133" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -12972,10 +12745,8 @@
       <c r="AS133" s="1"/>
       <c r="AT133" s="1"/>
       <c r="AU133" s="1"/>
-      <c r="AV133" s="1"/>
-      <c r="AW133" s="1"/>
-    </row>
-    <row r="134" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -13023,10 +12794,8 @@
       <c r="AS134" s="1"/>
       <c r="AT134" s="1"/>
       <c r="AU134" s="1"/>
-      <c r="AV134" s="1"/>
-      <c r="AW134" s="1"/>
-    </row>
-    <row r="135" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -13074,10 +12843,8 @@
       <c r="AS135" s="1"/>
       <c r="AT135" s="1"/>
       <c r="AU135" s="1"/>
-      <c r="AV135" s="1"/>
-      <c r="AW135" s="1"/>
-    </row>
-    <row r="136" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -13125,10 +12892,8 @@
       <c r="AS136" s="1"/>
       <c r="AT136" s="1"/>
       <c r="AU136" s="1"/>
-      <c r="AV136" s="1"/>
-      <c r="AW136" s="1"/>
-    </row>
-    <row r="137" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -13176,10 +12941,8 @@
       <c r="AS137" s="1"/>
       <c r="AT137" s="1"/>
       <c r="AU137" s="1"/>
-      <c r="AV137" s="1"/>
-      <c r="AW137" s="1"/>
-    </row>
-    <row r="138" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -13227,10 +12990,8 @@
       <c r="AS138" s="1"/>
       <c r="AT138" s="1"/>
       <c r="AU138" s="1"/>
-      <c r="AV138" s="1"/>
-      <c r="AW138" s="1"/>
-    </row>
-    <row r="139" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -13278,10 +13039,8 @@
       <c r="AS139" s="1"/>
       <c r="AT139" s="1"/>
       <c r="AU139" s="1"/>
-      <c r="AV139" s="1"/>
-      <c r="AW139" s="1"/>
-    </row>
-    <row r="140" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -13329,10 +13088,8 @@
       <c r="AS140" s="1"/>
       <c r="AT140" s="1"/>
       <c r="AU140" s="1"/>
-      <c r="AV140" s="1"/>
-      <c r="AW140" s="1"/>
-    </row>
-    <row r="141" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -13380,10 +13137,8 @@
       <c r="AS141" s="1"/>
       <c r="AT141" s="1"/>
       <c r="AU141" s="1"/>
-      <c r="AV141" s="1"/>
-      <c r="AW141" s="1"/>
-    </row>
-    <row r="142" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -13431,10 +13186,8 @@
       <c r="AS142" s="1"/>
       <c r="AT142" s="1"/>
       <c r="AU142" s="1"/>
-      <c r="AV142" s="1"/>
-      <c r="AW142" s="1"/>
-    </row>
-    <row r="143" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -13482,10 +13235,8 @@
       <c r="AS143" s="1"/>
       <c r="AT143" s="1"/>
       <c r="AU143" s="1"/>
-      <c r="AV143" s="1"/>
-      <c r="AW143" s="1"/>
-    </row>
-    <row r="144" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -13533,10 +13284,8 @@
       <c r="AS144" s="1"/>
       <c r="AT144" s="1"/>
       <c r="AU144" s="1"/>
-      <c r="AV144" s="1"/>
-      <c r="AW144" s="1"/>
-    </row>
-    <row r="145" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -13584,10 +13333,8 @@
       <c r="AS145" s="1"/>
       <c r="AT145" s="1"/>
       <c r="AU145" s="1"/>
-      <c r="AV145" s="1"/>
-      <c r="AW145" s="1"/>
-    </row>
-    <row r="146" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -13635,10 +13382,8 @@
       <c r="AS146" s="1"/>
       <c r="AT146" s="1"/>
       <c r="AU146" s="1"/>
-      <c r="AV146" s="1"/>
-      <c r="AW146" s="1"/>
-    </row>
-    <row r="147" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -13686,10 +13431,8 @@
       <c r="AS147" s="1"/>
       <c r="AT147" s="1"/>
       <c r="AU147" s="1"/>
-      <c r="AV147" s="1"/>
-      <c r="AW147" s="1"/>
-    </row>
-    <row r="148" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -13737,10 +13480,8 @@
       <c r="AS148" s="1"/>
       <c r="AT148" s="1"/>
       <c r="AU148" s="1"/>
-      <c r="AV148" s="1"/>
-      <c r="AW148" s="1"/>
-    </row>
-    <row r="149" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -13788,10 +13529,8 @@
       <c r="AS149" s="1"/>
       <c r="AT149" s="1"/>
       <c r="AU149" s="1"/>
-      <c r="AV149" s="1"/>
-      <c r="AW149" s="1"/>
-    </row>
-    <row r="150" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -13839,10 +13578,8 @@
       <c r="AS150" s="1"/>
       <c r="AT150" s="1"/>
       <c r="AU150" s="1"/>
-      <c r="AV150" s="1"/>
-      <c r="AW150" s="1"/>
-    </row>
-    <row r="151" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -13890,10 +13627,8 @@
       <c r="AS151" s="1"/>
       <c r="AT151" s="1"/>
       <c r="AU151" s="1"/>
-      <c r="AV151" s="1"/>
-      <c r="AW151" s="1"/>
-    </row>
-    <row r="152" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -13941,10 +13676,8 @@
       <c r="AS152" s="1"/>
       <c r="AT152" s="1"/>
       <c r="AU152" s="1"/>
-      <c r="AV152" s="1"/>
-      <c r="AW152" s="1"/>
-    </row>
-    <row r="153" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -13992,10 +13725,8 @@
       <c r="AS153" s="1"/>
       <c r="AT153" s="1"/>
       <c r="AU153" s="1"/>
-      <c r="AV153" s="1"/>
-      <c r="AW153" s="1"/>
-    </row>
-    <row r="154" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -14043,10 +13774,8 @@
       <c r="AS154" s="1"/>
       <c r="AT154" s="1"/>
       <c r="AU154" s="1"/>
-      <c r="AV154" s="1"/>
-      <c r="AW154" s="1"/>
-    </row>
-    <row r="155" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -14094,10 +13823,8 @@
       <c r="AS155" s="1"/>
       <c r="AT155" s="1"/>
       <c r="AU155" s="1"/>
-      <c r="AV155" s="1"/>
-      <c r="AW155" s="1"/>
-    </row>
-    <row r="156" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -14145,10 +13872,8 @@
       <c r="AS156" s="1"/>
       <c r="AT156" s="1"/>
       <c r="AU156" s="1"/>
-      <c r="AV156" s="1"/>
-      <c r="AW156" s="1"/>
-    </row>
-    <row r="157" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -14196,10 +13921,8 @@
       <c r="AS157" s="1"/>
       <c r="AT157" s="1"/>
       <c r="AU157" s="1"/>
-      <c r="AV157" s="1"/>
-      <c r="AW157" s="1"/>
-    </row>
-    <row r="158" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -14247,10 +13970,8 @@
       <c r="AS158" s="1"/>
       <c r="AT158" s="1"/>
       <c r="AU158" s="1"/>
-      <c r="AV158" s="1"/>
-      <c r="AW158" s="1"/>
-    </row>
-    <row r="159" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -14298,10 +14019,8 @@
       <c r="AS159" s="1"/>
       <c r="AT159" s="1"/>
       <c r="AU159" s="1"/>
-      <c r="AV159" s="1"/>
-      <c r="AW159" s="1"/>
-    </row>
-    <row r="160" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -14349,10 +14068,8 @@
       <c r="AS160" s="1"/>
       <c r="AT160" s="1"/>
       <c r="AU160" s="1"/>
-      <c r="AV160" s="1"/>
-      <c r="AW160" s="1"/>
-    </row>
-    <row r="161" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -14400,10 +14117,8 @@
       <c r="AS161" s="1"/>
       <c r="AT161" s="1"/>
       <c r="AU161" s="1"/>
-      <c r="AV161" s="1"/>
-      <c r="AW161" s="1"/>
-    </row>
-    <row r="162" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -14451,10 +14166,8 @@
       <c r="AS162" s="1"/>
       <c r="AT162" s="1"/>
       <c r="AU162" s="1"/>
-      <c r="AV162" s="1"/>
-      <c r="AW162" s="1"/>
-    </row>
-    <row r="163" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -14502,10 +14215,8 @@
       <c r="AS163" s="1"/>
       <c r="AT163" s="1"/>
       <c r="AU163" s="1"/>
-      <c r="AV163" s="1"/>
-      <c r="AW163" s="1"/>
-    </row>
-    <row r="164" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -14553,10 +14264,8 @@
       <c r="AS164" s="1"/>
       <c r="AT164" s="1"/>
       <c r="AU164" s="1"/>
-      <c r="AV164" s="1"/>
-      <c r="AW164" s="1"/>
-    </row>
-    <row r="165" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -14604,10 +14313,8 @@
       <c r="AS165" s="1"/>
       <c r="AT165" s="1"/>
       <c r="AU165" s="1"/>
-      <c r="AV165" s="1"/>
-      <c r="AW165" s="1"/>
-    </row>
-    <row r="166" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -14655,10 +14362,8 @@
       <c r="AS166" s="1"/>
       <c r="AT166" s="1"/>
       <c r="AU166" s="1"/>
-      <c r="AV166" s="1"/>
-      <c r="AW166" s="1"/>
-    </row>
-    <row r="167" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -14706,10 +14411,8 @@
       <c r="AS167" s="1"/>
       <c r="AT167" s="1"/>
       <c r="AU167" s="1"/>
-      <c r="AV167" s="1"/>
-      <c r="AW167" s="1"/>
-    </row>
-    <row r="168" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -14757,10 +14460,8 @@
       <c r="AS168" s="1"/>
       <c r="AT168" s="1"/>
       <c r="AU168" s="1"/>
-      <c r="AV168" s="1"/>
-      <c r="AW168" s="1"/>
-    </row>
-    <row r="169" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -14808,10 +14509,8 @@
       <c r="AS169" s="1"/>
       <c r="AT169" s="1"/>
       <c r="AU169" s="1"/>
-      <c r="AV169" s="1"/>
-      <c r="AW169" s="1"/>
-    </row>
-    <row r="170" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -14859,10 +14558,8 @@
       <c r="AS170" s="1"/>
       <c r="AT170" s="1"/>
       <c r="AU170" s="1"/>
-      <c r="AV170" s="1"/>
-      <c r="AW170" s="1"/>
-    </row>
-    <row r="171" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -14910,10 +14607,8 @@
       <c r="AS171" s="1"/>
       <c r="AT171" s="1"/>
       <c r="AU171" s="1"/>
-      <c r="AV171" s="1"/>
-      <c r="AW171" s="1"/>
-    </row>
-    <row r="172" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -14961,10 +14656,8 @@
       <c r="AS172" s="1"/>
       <c r="AT172" s="1"/>
       <c r="AU172" s="1"/>
-      <c r="AV172" s="1"/>
-      <c r="AW172" s="1"/>
-    </row>
-    <row r="173" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -15012,10 +14705,8 @@
       <c r="AS173" s="1"/>
       <c r="AT173" s="1"/>
       <c r="AU173" s="1"/>
-      <c r="AV173" s="1"/>
-      <c r="AW173" s="1"/>
-    </row>
-    <row r="174" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -15063,10 +14754,8 @@
       <c r="AS174" s="1"/>
       <c r="AT174" s="1"/>
       <c r="AU174" s="1"/>
-      <c r="AV174" s="1"/>
-      <c r="AW174" s="1"/>
-    </row>
-    <row r="175" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -15114,10 +14803,8 @@
       <c r="AS175" s="1"/>
       <c r="AT175" s="1"/>
       <c r="AU175" s="1"/>
-      <c r="AV175" s="1"/>
-      <c r="AW175" s="1"/>
-    </row>
-    <row r="176" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -15165,10 +14852,8 @@
       <c r="AS176" s="1"/>
       <c r="AT176" s="1"/>
       <c r="AU176" s="1"/>
-      <c r="AV176" s="1"/>
-      <c r="AW176" s="1"/>
-    </row>
-    <row r="177" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -15216,10 +14901,8 @@
       <c r="AS177" s="1"/>
       <c r="AT177" s="1"/>
       <c r="AU177" s="1"/>
-      <c r="AV177" s="1"/>
-      <c r="AW177" s="1"/>
-    </row>
-    <row r="178" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -15267,10 +14950,8 @@
       <c r="AS178" s="1"/>
       <c r="AT178" s="1"/>
       <c r="AU178" s="1"/>
-      <c r="AV178" s="1"/>
-      <c r="AW178" s="1"/>
-    </row>
-    <row r="179" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -15318,10 +14999,8 @@
       <c r="AS179" s="1"/>
       <c r="AT179" s="1"/>
       <c r="AU179" s="1"/>
-      <c r="AV179" s="1"/>
-      <c r="AW179" s="1"/>
-    </row>
-    <row r="180" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -15369,10 +15048,8 @@
       <c r="AS180" s="1"/>
       <c r="AT180" s="1"/>
       <c r="AU180" s="1"/>
-      <c r="AV180" s="1"/>
-      <c r="AW180" s="1"/>
-    </row>
-    <row r="181" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -15420,10 +15097,8 @@
       <c r="AS181" s="1"/>
       <c r="AT181" s="1"/>
       <c r="AU181" s="1"/>
-      <c r="AV181" s="1"/>
-      <c r="AW181" s="1"/>
-    </row>
-    <row r="182" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -15471,10 +15146,8 @@
       <c r="AS182" s="1"/>
       <c r="AT182" s="1"/>
       <c r="AU182" s="1"/>
-      <c r="AV182" s="1"/>
-      <c r="AW182" s="1"/>
-    </row>
-    <row r="183" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -15522,10 +15195,8 @@
       <c r="AS183" s="1"/>
       <c r="AT183" s="1"/>
       <c r="AU183" s="1"/>
-      <c r="AV183" s="1"/>
-      <c r="AW183" s="1"/>
-    </row>
-    <row r="184" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -15573,10 +15244,8 @@
       <c r="AS184" s="1"/>
       <c r="AT184" s="1"/>
       <c r="AU184" s="1"/>
-      <c r="AV184" s="1"/>
-      <c r="AW184" s="1"/>
-    </row>
-    <row r="185" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -15624,10 +15293,8 @@
       <c r="AS185" s="1"/>
       <c r="AT185" s="1"/>
       <c r="AU185" s="1"/>
-      <c r="AV185" s="1"/>
-      <c r="AW185" s="1"/>
-    </row>
-    <row r="186" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -15675,10 +15342,8 @@
       <c r="AS186" s="1"/>
       <c r="AT186" s="1"/>
       <c r="AU186" s="1"/>
-      <c r="AV186" s="1"/>
-      <c r="AW186" s="1"/>
-    </row>
-    <row r="187" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -15726,10 +15391,8 @@
       <c r="AS187" s="1"/>
       <c r="AT187" s="1"/>
       <c r="AU187" s="1"/>
-      <c r="AV187" s="1"/>
-      <c r="AW187" s="1"/>
-    </row>
-    <row r="188" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -15777,10 +15440,8 @@
       <c r="AS188" s="1"/>
       <c r="AT188" s="1"/>
       <c r="AU188" s="1"/>
-      <c r="AV188" s="1"/>
-      <c r="AW188" s="1"/>
-    </row>
-    <row r="189" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -15828,10 +15489,8 @@
       <c r="AS189" s="1"/>
       <c r="AT189" s="1"/>
       <c r="AU189" s="1"/>
-      <c r="AV189" s="1"/>
-      <c r="AW189" s="1"/>
-    </row>
-    <row r="190" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -15879,10 +15538,8 @@
       <c r="AS190" s="1"/>
       <c r="AT190" s="1"/>
       <c r="AU190" s="1"/>
-      <c r="AV190" s="1"/>
-      <c r="AW190" s="1"/>
-    </row>
-    <row r="191" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -15930,10 +15587,8 @@
       <c r="AS191" s="1"/>
       <c r="AT191" s="1"/>
       <c r="AU191" s="1"/>
-      <c r="AV191" s="1"/>
-      <c r="AW191" s="1"/>
-    </row>
-    <row r="192" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -15981,10 +15636,8 @@
       <c r="AS192" s="1"/>
       <c r="AT192" s="1"/>
       <c r="AU192" s="1"/>
-      <c r="AV192" s="1"/>
-      <c r="AW192" s="1"/>
-    </row>
-    <row r="193" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -16032,10 +15685,8 @@
       <c r="AS193" s="1"/>
       <c r="AT193" s="1"/>
       <c r="AU193" s="1"/>
-      <c r="AV193" s="1"/>
-      <c r="AW193" s="1"/>
-    </row>
-    <row r="194" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -16083,10 +15734,8 @@
       <c r="AS194" s="1"/>
       <c r="AT194" s="1"/>
       <c r="AU194" s="1"/>
-      <c r="AV194" s="1"/>
-      <c r="AW194" s="1"/>
-    </row>
-    <row r="195" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -16134,10 +15783,8 @@
       <c r="AS195" s="1"/>
       <c r="AT195" s="1"/>
       <c r="AU195" s="1"/>
-      <c r="AV195" s="1"/>
-      <c r="AW195" s="1"/>
-    </row>
-    <row r="196" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -16185,10 +15832,8 @@
       <c r="AS196" s="1"/>
       <c r="AT196" s="1"/>
       <c r="AU196" s="1"/>
-      <c r="AV196" s="1"/>
-      <c r="AW196" s="1"/>
-    </row>
-    <row r="197" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -16236,10 +15881,8 @@
       <c r="AS197" s="1"/>
       <c r="AT197" s="1"/>
       <c r="AU197" s="1"/>
-      <c r="AV197" s="1"/>
-      <c r="AW197" s="1"/>
-    </row>
-    <row r="198" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -16287,10 +15930,8 @@
       <c r="AS198" s="1"/>
       <c r="AT198" s="1"/>
       <c r="AU198" s="1"/>
-      <c r="AV198" s="1"/>
-      <c r="AW198" s="1"/>
-    </row>
-    <row r="199" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -16338,10 +15979,8 @@
       <c r="AS199" s="1"/>
       <c r="AT199" s="1"/>
       <c r="AU199" s="1"/>
-      <c r="AV199" s="1"/>
-      <c r="AW199" s="1"/>
-    </row>
-    <row r="200" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -16389,10 +16028,8 @@
       <c r="AS200" s="1"/>
       <c r="AT200" s="1"/>
       <c r="AU200" s="1"/>
-      <c r="AV200" s="1"/>
-      <c r="AW200" s="1"/>
-    </row>
-    <row r="201" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -16440,10 +16077,8 @@
       <c r="AS201" s="1"/>
       <c r="AT201" s="1"/>
       <c r="AU201" s="1"/>
-      <c r="AV201" s="1"/>
-      <c r="AW201" s="1"/>
-    </row>
-    <row r="202" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -16491,10 +16126,8 @@
       <c r="AS202" s="1"/>
       <c r="AT202" s="1"/>
       <c r="AU202" s="1"/>
-      <c r="AV202" s="1"/>
-      <c r="AW202" s="1"/>
-    </row>
-    <row r="203" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -16542,10 +16175,8 @@
       <c r="AS203" s="1"/>
       <c r="AT203" s="1"/>
       <c r="AU203" s="1"/>
-      <c r="AV203" s="1"/>
-      <c r="AW203" s="1"/>
-    </row>
-    <row r="204" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -16593,10 +16224,8 @@
       <c r="AS204" s="1"/>
       <c r="AT204" s="1"/>
       <c r="AU204" s="1"/>
-      <c r="AV204" s="1"/>
-      <c r="AW204" s="1"/>
-    </row>
-    <row r="205" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -16644,10 +16273,8 @@
       <c r="AS205" s="1"/>
       <c r="AT205" s="1"/>
       <c r="AU205" s="1"/>
-      <c r="AV205" s="1"/>
-      <c r="AW205" s="1"/>
-    </row>
-    <row r="206" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -16695,10 +16322,8 @@
       <c r="AS206" s="1"/>
       <c r="AT206" s="1"/>
       <c r="AU206" s="1"/>
-      <c r="AV206" s="1"/>
-      <c r="AW206" s="1"/>
-    </row>
-    <row r="207" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -16746,10 +16371,8 @@
       <c r="AS207" s="1"/>
       <c r="AT207" s="1"/>
       <c r="AU207" s="1"/>
-      <c r="AV207" s="1"/>
-      <c r="AW207" s="1"/>
-    </row>
-    <row r="208" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -16797,10 +16420,8 @@
       <c r="AS208" s="1"/>
       <c r="AT208" s="1"/>
       <c r="AU208" s="1"/>
-      <c r="AV208" s="1"/>
-      <c r="AW208" s="1"/>
-    </row>
-    <row r="209" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -16848,10 +16469,8 @@
       <c r="AS209" s="1"/>
       <c r="AT209" s="1"/>
       <c r="AU209" s="1"/>
-      <c r="AV209" s="1"/>
-      <c r="AW209" s="1"/>
-    </row>
-    <row r="210" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -16899,10 +16518,8 @@
       <c r="AS210" s="1"/>
       <c r="AT210" s="1"/>
       <c r="AU210" s="1"/>
-      <c r="AV210" s="1"/>
-      <c r="AW210" s="1"/>
-    </row>
-    <row r="211" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -16950,10 +16567,8 @@
       <c r="AS211" s="1"/>
       <c r="AT211" s="1"/>
       <c r="AU211" s="1"/>
-      <c r="AV211" s="1"/>
-      <c r="AW211" s="1"/>
-    </row>
-    <row r="212" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -17001,10 +16616,8 @@
       <c r="AS212" s="1"/>
       <c r="AT212" s="1"/>
       <c r="AU212" s="1"/>
-      <c r="AV212" s="1"/>
-      <c r="AW212" s="1"/>
-    </row>
-    <row r="213" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -17052,10 +16665,8 @@
       <c r="AS213" s="1"/>
       <c r="AT213" s="1"/>
       <c r="AU213" s="1"/>
-      <c r="AV213" s="1"/>
-      <c r="AW213" s="1"/>
-    </row>
-    <row r="214" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -17103,10 +16714,8 @@
       <c r="AS214" s="1"/>
       <c r="AT214" s="1"/>
       <c r="AU214" s="1"/>
-      <c r="AV214" s="1"/>
-      <c r="AW214" s="1"/>
-    </row>
-    <row r="215" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -17154,10 +16763,8 @@
       <c r="AS215" s="1"/>
       <c r="AT215" s="1"/>
       <c r="AU215" s="1"/>
-      <c r="AV215" s="1"/>
-      <c r="AW215" s="1"/>
-    </row>
-    <row r="216" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -17205,10 +16812,8 @@
       <c r="AS216" s="1"/>
       <c r="AT216" s="1"/>
       <c r="AU216" s="1"/>
-      <c r="AV216" s="1"/>
-      <c r="AW216" s="1"/>
-    </row>
-    <row r="217" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -17256,10 +16861,8 @@
       <c r="AS217" s="1"/>
       <c r="AT217" s="1"/>
       <c r="AU217" s="1"/>
-      <c r="AV217" s="1"/>
-      <c r="AW217" s="1"/>
-    </row>
-    <row r="218" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -17307,10 +16910,8 @@
       <c r="AS218" s="1"/>
       <c r="AT218" s="1"/>
       <c r="AU218" s="1"/>
-      <c r="AV218" s="1"/>
-      <c r="AW218" s="1"/>
-    </row>
-    <row r="219" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -17358,10 +16959,8 @@
       <c r="AS219" s="1"/>
       <c r="AT219" s="1"/>
       <c r="AU219" s="1"/>
-      <c r="AV219" s="1"/>
-      <c r="AW219" s="1"/>
-    </row>
-    <row r="220" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -17409,10 +17008,8 @@
       <c r="AS220" s="1"/>
       <c r="AT220" s="1"/>
       <c r="AU220" s="1"/>
-      <c r="AV220" s="1"/>
-      <c r="AW220" s="1"/>
-    </row>
-    <row r="221" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -17460,10 +17057,8 @@
       <c r="AS221" s="1"/>
       <c r="AT221" s="1"/>
       <c r="AU221" s="1"/>
-      <c r="AV221" s="1"/>
-      <c r="AW221" s="1"/>
-    </row>
-    <row r="222" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -17511,10 +17106,8 @@
       <c r="AS222" s="1"/>
       <c r="AT222" s="1"/>
       <c r="AU222" s="1"/>
-      <c r="AV222" s="1"/>
-      <c r="AW222" s="1"/>
-    </row>
-    <row r="223" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -17562,10 +17155,8 @@
       <c r="AS223" s="1"/>
       <c r="AT223" s="1"/>
       <c r="AU223" s="1"/>
-      <c r="AV223" s="1"/>
-      <c r="AW223" s="1"/>
-    </row>
-    <row r="224" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -17613,10 +17204,8 @@
       <c r="AS224" s="1"/>
       <c r="AT224" s="1"/>
       <c r="AU224" s="1"/>
-      <c r="AV224" s="1"/>
-      <c r="AW224" s="1"/>
-    </row>
-    <row r="225" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -17664,10 +17253,8 @@
       <c r="AS225" s="1"/>
       <c r="AT225" s="1"/>
       <c r="AU225" s="1"/>
-      <c r="AV225" s="1"/>
-      <c r="AW225" s="1"/>
-    </row>
-    <row r="226" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -17715,10 +17302,8 @@
       <c r="AS226" s="1"/>
       <c r="AT226" s="1"/>
       <c r="AU226" s="1"/>
-      <c r="AV226" s="1"/>
-      <c r="AW226" s="1"/>
-    </row>
-    <row r="227" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -17766,10 +17351,8 @@
       <c r="AS227" s="1"/>
       <c r="AT227" s="1"/>
       <c r="AU227" s="1"/>
-      <c r="AV227" s="1"/>
-      <c r="AW227" s="1"/>
-    </row>
-    <row r="228" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -17817,10 +17400,8 @@
       <c r="AS228" s="1"/>
       <c r="AT228" s="1"/>
       <c r="AU228" s="1"/>
-      <c r="AV228" s="1"/>
-      <c r="AW228" s="1"/>
-    </row>
-    <row r="229" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -17868,10 +17449,8 @@
       <c r="AS229" s="1"/>
       <c r="AT229" s="1"/>
       <c r="AU229" s="1"/>
-      <c r="AV229" s="1"/>
-      <c r="AW229" s="1"/>
-    </row>
-    <row r="230" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -17919,10 +17498,8 @@
       <c r="AS230" s="1"/>
       <c r="AT230" s="1"/>
       <c r="AU230" s="1"/>
-      <c r="AV230" s="1"/>
-      <c r="AW230" s="1"/>
-    </row>
-    <row r="231" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -17970,10 +17547,8 @@
       <c r="AS231" s="1"/>
       <c r="AT231" s="1"/>
       <c r="AU231" s="1"/>
-      <c r="AV231" s="1"/>
-      <c r="AW231" s="1"/>
-    </row>
-    <row r="232" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -18021,10 +17596,8 @@
       <c r="AS232" s="1"/>
       <c r="AT232" s="1"/>
       <c r="AU232" s="1"/>
-      <c r="AV232" s="1"/>
-      <c r="AW232" s="1"/>
-    </row>
-    <row r="233" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -18072,10 +17645,8 @@
       <c r="AS233" s="1"/>
       <c r="AT233" s="1"/>
       <c r="AU233" s="1"/>
-      <c r="AV233" s="1"/>
-      <c r="AW233" s="1"/>
-    </row>
-    <row r="234" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -18123,10 +17694,8 @@
       <c r="AS234" s="1"/>
       <c r="AT234" s="1"/>
       <c r="AU234" s="1"/>
-      <c r="AV234" s="1"/>
-      <c r="AW234" s="1"/>
-    </row>
-    <row r="235" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -18174,10 +17743,8 @@
       <c r="AS235" s="1"/>
       <c r="AT235" s="1"/>
       <c r="AU235" s="1"/>
-      <c r="AV235" s="1"/>
-      <c r="AW235" s="1"/>
-    </row>
-    <row r="236" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -18225,10 +17792,8 @@
       <c r="AS236" s="1"/>
       <c r="AT236" s="1"/>
       <c r="AU236" s="1"/>
-      <c r="AV236" s="1"/>
-      <c r="AW236" s="1"/>
-    </row>
-    <row r="237" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -18276,10 +17841,8 @@
       <c r="AS237" s="1"/>
       <c r="AT237" s="1"/>
       <c r="AU237" s="1"/>
-      <c r="AV237" s="1"/>
-      <c r="AW237" s="1"/>
-    </row>
-    <row r="238" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -18327,10 +17890,8 @@
       <c r="AS238" s="1"/>
       <c r="AT238" s="1"/>
       <c r="AU238" s="1"/>
-      <c r="AV238" s="1"/>
-      <c r="AW238" s="1"/>
-    </row>
-    <row r="239" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -18378,10 +17939,8 @@
       <c r="AS239" s="1"/>
       <c r="AT239" s="1"/>
       <c r="AU239" s="1"/>
-      <c r="AV239" s="1"/>
-      <c r="AW239" s="1"/>
-    </row>
-    <row r="240" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -18429,10 +17988,8 @@
       <c r="AS240" s="1"/>
       <c r="AT240" s="1"/>
       <c r="AU240" s="1"/>
-      <c r="AV240" s="1"/>
-      <c r="AW240" s="1"/>
-    </row>
-    <row r="241" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -18480,10 +18037,8 @@
       <c r="AS241" s="1"/>
       <c r="AT241" s="1"/>
       <c r="AU241" s="1"/>
-      <c r="AV241" s="1"/>
-      <c r="AW241" s="1"/>
-    </row>
-    <row r="242" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -18531,10 +18086,8 @@
       <c r="AS242" s="1"/>
       <c r="AT242" s="1"/>
       <c r="AU242" s="1"/>
-      <c r="AV242" s="1"/>
-      <c r="AW242" s="1"/>
-    </row>
-    <row r="243" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -18582,10 +18135,8 @@
       <c r="AS243" s="1"/>
       <c r="AT243" s="1"/>
       <c r="AU243" s="1"/>
-      <c r="AV243" s="1"/>
-      <c r="AW243" s="1"/>
-    </row>
-    <row r="244" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -18633,10 +18184,8 @@
       <c r="AS244" s="1"/>
       <c r="AT244" s="1"/>
       <c r="AU244" s="1"/>
-      <c r="AV244" s="1"/>
-      <c r="AW244" s="1"/>
-    </row>
-    <row r="245" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -18684,10 +18233,8 @@
       <c r="AS245" s="1"/>
       <c r="AT245" s="1"/>
       <c r="AU245" s="1"/>
-      <c r="AV245" s="1"/>
-      <c r="AW245" s="1"/>
-    </row>
-    <row r="246" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -18735,10 +18282,8 @@
       <c r="AS246" s="1"/>
       <c r="AT246" s="1"/>
       <c r="AU246" s="1"/>
-      <c r="AV246" s="1"/>
-      <c r="AW246" s="1"/>
-    </row>
-    <row r="247" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -18786,10 +18331,8 @@
       <c r="AS247" s="1"/>
       <c r="AT247" s="1"/>
       <c r="AU247" s="1"/>
-      <c r="AV247" s="1"/>
-      <c r="AW247" s="1"/>
-    </row>
-    <row r="248" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -18837,10 +18380,8 @@
       <c r="AS248" s="1"/>
       <c r="AT248" s="1"/>
       <c r="AU248" s="1"/>
-      <c r="AV248" s="1"/>
-      <c r="AW248" s="1"/>
-    </row>
-    <row r="249" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -18888,10 +18429,8 @@
       <c r="AS249" s="1"/>
       <c r="AT249" s="1"/>
       <c r="AU249" s="1"/>
-      <c r="AV249" s="1"/>
-      <c r="AW249" s="1"/>
-    </row>
-    <row r="250" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -18939,10 +18478,8 @@
       <c r="AS250" s="1"/>
       <c r="AT250" s="1"/>
       <c r="AU250" s="1"/>
-      <c r="AV250" s="1"/>
-      <c r="AW250" s="1"/>
-    </row>
-    <row r="251" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -18990,10 +18527,8 @@
       <c r="AS251" s="1"/>
       <c r="AT251" s="1"/>
       <c r="AU251" s="1"/>
-      <c r="AV251" s="1"/>
-      <c r="AW251" s="1"/>
-    </row>
-    <row r="252" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -19041,10 +18576,8 @@
       <c r="AS252" s="1"/>
       <c r="AT252" s="1"/>
       <c r="AU252" s="1"/>
-      <c r="AV252" s="1"/>
-      <c r="AW252" s="1"/>
-    </row>
-    <row r="253" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -19092,10 +18625,8 @@
       <c r="AS253" s="1"/>
       <c r="AT253" s="1"/>
       <c r="AU253" s="1"/>
-      <c r="AV253" s="1"/>
-      <c r="AW253" s="1"/>
-    </row>
-    <row r="254" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -19143,10 +18674,8 @@
       <c r="AS254" s="1"/>
       <c r="AT254" s="1"/>
       <c r="AU254" s="1"/>
-      <c r="AV254" s="1"/>
-      <c r="AW254" s="1"/>
-    </row>
-    <row r="255" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -19194,10 +18723,8 @@
       <c r="AS255" s="1"/>
       <c r="AT255" s="1"/>
       <c r="AU255" s="1"/>
-      <c r="AV255" s="1"/>
-      <c r="AW255" s="1"/>
-    </row>
-    <row r="256" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -19245,10 +18772,8 @@
       <c r="AS256" s="1"/>
       <c r="AT256" s="1"/>
       <c r="AU256" s="1"/>
-      <c r="AV256" s="1"/>
-      <c r="AW256" s="1"/>
-    </row>
-    <row r="257" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -19296,10 +18821,8 @@
       <c r="AS257" s="1"/>
       <c r="AT257" s="1"/>
       <c r="AU257" s="1"/>
-      <c r="AV257" s="1"/>
-      <c r="AW257" s="1"/>
-    </row>
-    <row r="258" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -19347,10 +18870,8 @@
       <c r="AS258" s="1"/>
       <c r="AT258" s="1"/>
       <c r="AU258" s="1"/>
-      <c r="AV258" s="1"/>
-      <c r="AW258" s="1"/>
-    </row>
-    <row r="259" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -19398,10 +18919,8 @@
       <c r="AS259" s="1"/>
       <c r="AT259" s="1"/>
       <c r="AU259" s="1"/>
-      <c r="AV259" s="1"/>
-      <c r="AW259" s="1"/>
-    </row>
-    <row r="260" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -19449,10 +18968,8 @@
       <c r="AS260" s="1"/>
       <c r="AT260" s="1"/>
       <c r="AU260" s="1"/>
-      <c r="AV260" s="1"/>
-      <c r="AW260" s="1"/>
-    </row>
-    <row r="261" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -19500,10 +19017,8 @@
       <c r="AS261" s="1"/>
       <c r="AT261" s="1"/>
       <c r="AU261" s="1"/>
-      <c r="AV261" s="1"/>
-      <c r="AW261" s="1"/>
-    </row>
-    <row r="262" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -19551,10 +19066,8 @@
       <c r="AS262" s="1"/>
       <c r="AT262" s="1"/>
       <c r="AU262" s="1"/>
-      <c r="AV262" s="1"/>
-      <c r="AW262" s="1"/>
-    </row>
-    <row r="263" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -19602,10 +19115,8 @@
       <c r="AS263" s="1"/>
       <c r="AT263" s="1"/>
       <c r="AU263" s="1"/>
-      <c r="AV263" s="1"/>
-      <c r="AW263" s="1"/>
-    </row>
-    <row r="264" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="264" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -19653,10 +19164,8 @@
       <c r="AS264" s="1"/>
       <c r="AT264" s="1"/>
       <c r="AU264" s="1"/>
-      <c r="AV264" s="1"/>
-      <c r="AW264" s="1"/>
-    </row>
-    <row r="265" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -19704,10 +19213,8 @@
       <c r="AS265" s="1"/>
       <c r="AT265" s="1"/>
       <c r="AU265" s="1"/>
-      <c r="AV265" s="1"/>
-      <c r="AW265" s="1"/>
-    </row>
-    <row r="266" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -19755,10 +19262,8 @@
       <c r="AS266" s="1"/>
       <c r="AT266" s="1"/>
       <c r="AU266" s="1"/>
-      <c r="AV266" s="1"/>
-      <c r="AW266" s="1"/>
-    </row>
-    <row r="267" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -19806,10 +19311,8 @@
       <c r="AS267" s="1"/>
       <c r="AT267" s="1"/>
       <c r="AU267" s="1"/>
-      <c r="AV267" s="1"/>
-      <c r="AW267" s="1"/>
-    </row>
-    <row r="268" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -19857,10 +19360,8 @@
       <c r="AS268" s="1"/>
       <c r="AT268" s="1"/>
       <c r="AU268" s="1"/>
-      <c r="AV268" s="1"/>
-      <c r="AW268" s="1"/>
-    </row>
-    <row r="269" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -19908,10 +19409,8 @@
       <c r="AS269" s="1"/>
       <c r="AT269" s="1"/>
       <c r="AU269" s="1"/>
-      <c r="AV269" s="1"/>
-      <c r="AW269" s="1"/>
-    </row>
-    <row r="270" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -19959,10 +19458,8 @@
       <c r="AS270" s="1"/>
       <c r="AT270" s="1"/>
       <c r="AU270" s="1"/>
-      <c r="AV270" s="1"/>
-      <c r="AW270" s="1"/>
-    </row>
-    <row r="271" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="271" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -20010,10 +19507,8 @@
       <c r="AS271" s="1"/>
       <c r="AT271" s="1"/>
       <c r="AU271" s="1"/>
-      <c r="AV271" s="1"/>
-      <c r="AW271" s="1"/>
-    </row>
-    <row r="272" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -20061,10 +19556,8 @@
       <c r="AS272" s="1"/>
       <c r="AT272" s="1"/>
       <c r="AU272" s="1"/>
-      <c r="AV272" s="1"/>
-      <c r="AW272" s="1"/>
-    </row>
-    <row r="273" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="273" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -20112,10 +19605,8 @@
       <c r="AS273" s="1"/>
       <c r="AT273" s="1"/>
       <c r="AU273" s="1"/>
-      <c r="AV273" s="1"/>
-      <c r="AW273" s="1"/>
-    </row>
-    <row r="274" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="274" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -20163,10 +19654,8 @@
       <c r="AS274" s="1"/>
       <c r="AT274" s="1"/>
       <c r="AU274" s="1"/>
-      <c r="AV274" s="1"/>
-      <c r="AW274" s="1"/>
-    </row>
-    <row r="275" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="275" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -20214,10 +19703,8 @@
       <c r="AS275" s="1"/>
       <c r="AT275" s="1"/>
       <c r="AU275" s="1"/>
-      <c r="AV275" s="1"/>
-      <c r="AW275" s="1"/>
-    </row>
-    <row r="276" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="276" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -20265,10 +19752,8 @@
       <c r="AS276" s="1"/>
       <c r="AT276" s="1"/>
       <c r="AU276" s="1"/>
-      <c r="AV276" s="1"/>
-      <c r="AW276" s="1"/>
-    </row>
-    <row r="277" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="277" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -20316,10 +19801,8 @@
       <c r="AS277" s="1"/>
       <c r="AT277" s="1"/>
       <c r="AU277" s="1"/>
-      <c r="AV277" s="1"/>
-      <c r="AW277" s="1"/>
-    </row>
-    <row r="278" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -20367,10 +19850,8 @@
       <c r="AS278" s="1"/>
       <c r="AT278" s="1"/>
       <c r="AU278" s="1"/>
-      <c r="AV278" s="1"/>
-      <c r="AW278" s="1"/>
-    </row>
-    <row r="279" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -20418,10 +19899,8 @@
       <c r="AS279" s="1"/>
       <c r="AT279" s="1"/>
       <c r="AU279" s="1"/>
-      <c r="AV279" s="1"/>
-      <c r="AW279" s="1"/>
-    </row>
-    <row r="280" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -20469,10 +19948,8 @@
       <c r="AS280" s="1"/>
       <c r="AT280" s="1"/>
       <c r="AU280" s="1"/>
-      <c r="AV280" s="1"/>
-      <c r="AW280" s="1"/>
-    </row>
-    <row r="281" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="281" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -20520,10 +19997,8 @@
       <c r="AS281" s="1"/>
       <c r="AT281" s="1"/>
       <c r="AU281" s="1"/>
-      <c r="AV281" s="1"/>
-      <c r="AW281" s="1"/>
-    </row>
-    <row r="282" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="282" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -20571,10 +20046,8 @@
       <c r="AS282" s="1"/>
       <c r="AT282" s="1"/>
       <c r="AU282" s="1"/>
-      <c r="AV282" s="1"/>
-      <c r="AW282" s="1"/>
-    </row>
-    <row r="283" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="283" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -20622,10 +20095,8 @@
       <c r="AS283" s="1"/>
       <c r="AT283" s="1"/>
       <c r="AU283" s="1"/>
-      <c r="AV283" s="1"/>
-      <c r="AW283" s="1"/>
-    </row>
-    <row r="284" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="284" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -20673,10 +20144,8 @@
       <c r="AS284" s="1"/>
       <c r="AT284" s="1"/>
       <c r="AU284" s="1"/>
-      <c r="AV284" s="1"/>
-      <c r="AW284" s="1"/>
-    </row>
-    <row r="285" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="285" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -20724,10 +20193,8 @@
       <c r="AS285" s="1"/>
       <c r="AT285" s="1"/>
       <c r="AU285" s="1"/>
-      <c r="AV285" s="1"/>
-      <c r="AW285" s="1"/>
-    </row>
-    <row r="286" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="286" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -20775,10 +20242,8 @@
       <c r="AS286" s="1"/>
       <c r="AT286" s="1"/>
       <c r="AU286" s="1"/>
-      <c r="AV286" s="1"/>
-      <c r="AW286" s="1"/>
-    </row>
-    <row r="287" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="287" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -20826,10 +20291,8 @@
       <c r="AS287" s="1"/>
       <c r="AT287" s="1"/>
       <c r="AU287" s="1"/>
-      <c r="AV287" s="1"/>
-      <c r="AW287" s="1"/>
-    </row>
-    <row r="288" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="288" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -20877,10 +20340,8 @@
       <c r="AS288" s="1"/>
       <c r="AT288" s="1"/>
       <c r="AU288" s="1"/>
-      <c r="AV288" s="1"/>
-      <c r="AW288" s="1"/>
-    </row>
-    <row r="289" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="289" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -20928,10 +20389,8 @@
       <c r="AS289" s="1"/>
       <c r="AT289" s="1"/>
       <c r="AU289" s="1"/>
-      <c r="AV289" s="1"/>
-      <c r="AW289" s="1"/>
-    </row>
-    <row r="290" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="290" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -20979,10 +20438,8 @@
       <c r="AS290" s="1"/>
       <c r="AT290" s="1"/>
       <c r="AU290" s="1"/>
-      <c r="AV290" s="1"/>
-      <c r="AW290" s="1"/>
-    </row>
-    <row r="291" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="291" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -21030,10 +20487,8 @@
       <c r="AS291" s="1"/>
       <c r="AT291" s="1"/>
       <c r="AU291" s="1"/>
-      <c r="AV291" s="1"/>
-      <c r="AW291" s="1"/>
-    </row>
-    <row r="292" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="292" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -21081,10 +20536,8 @@
       <c r="AS292" s="1"/>
       <c r="AT292" s="1"/>
       <c r="AU292" s="1"/>
-      <c r="AV292" s="1"/>
-      <c r="AW292" s="1"/>
-    </row>
-    <row r="293" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -21132,10 +20585,8 @@
       <c r="AS293" s="1"/>
       <c r="AT293" s="1"/>
       <c r="AU293" s="1"/>
-      <c r="AV293" s="1"/>
-      <c r="AW293" s="1"/>
-    </row>
-    <row r="294" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -21183,10 +20634,8 @@
       <c r="AS294" s="1"/>
       <c r="AT294" s="1"/>
       <c r="AU294" s="1"/>
-      <c r="AV294" s="1"/>
-      <c r="AW294" s="1"/>
-    </row>
-    <row r="295" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -21234,10 +20683,8 @@
       <c r="AS295" s="1"/>
       <c r="AT295" s="1"/>
       <c r="AU295" s="1"/>
-      <c r="AV295" s="1"/>
-      <c r="AW295" s="1"/>
-    </row>
-    <row r="296" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="296" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -21285,10 +20732,8 @@
       <c r="AS296" s="1"/>
       <c r="AT296" s="1"/>
       <c r="AU296" s="1"/>
-      <c r="AV296" s="1"/>
-      <c r="AW296" s="1"/>
-    </row>
-    <row r="297" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -21336,10 +20781,8 @@
       <c r="AS297" s="1"/>
       <c r="AT297" s="1"/>
       <c r="AU297" s="1"/>
-      <c r="AV297" s="1"/>
-      <c r="AW297" s="1"/>
-    </row>
-    <row r="298" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -21387,10 +20830,8 @@
       <c r="AS298" s="1"/>
       <c r="AT298" s="1"/>
       <c r="AU298" s="1"/>
-      <c r="AV298" s="1"/>
-      <c r="AW298" s="1"/>
-    </row>
-    <row r="299" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -21438,10 +20879,8 @@
       <c r="AS299" s="1"/>
       <c r="AT299" s="1"/>
       <c r="AU299" s="1"/>
-      <c r="AV299" s="1"/>
-      <c r="AW299" s="1"/>
-    </row>
-    <row r="300" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -21489,10 +20928,8 @@
       <c r="AS300" s="1"/>
       <c r="AT300" s="1"/>
       <c r="AU300" s="1"/>
-      <c r="AV300" s="1"/>
-      <c r="AW300" s="1"/>
-    </row>
-    <row r="301" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -21540,10 +20977,8 @@
       <c r="AS301" s="1"/>
       <c r="AT301" s="1"/>
       <c r="AU301" s="1"/>
-      <c r="AV301" s="1"/>
-      <c r="AW301" s="1"/>
-    </row>
-    <row r="302" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -21591,10 +21026,8 @@
       <c r="AS302" s="1"/>
       <c r="AT302" s="1"/>
       <c r="AU302" s="1"/>
-      <c r="AV302" s="1"/>
-      <c r="AW302" s="1"/>
-    </row>
-    <row r="303" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -21642,10 +21075,8 @@
       <c r="AS303" s="1"/>
       <c r="AT303" s="1"/>
       <c r="AU303" s="1"/>
-      <c r="AV303" s="1"/>
-      <c r="AW303" s="1"/>
-    </row>
-    <row r="304" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="304" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -21693,10 +21124,8 @@
       <c r="AS304" s="1"/>
       <c r="AT304" s="1"/>
       <c r="AU304" s="1"/>
-      <c r="AV304" s="1"/>
-      <c r="AW304" s="1"/>
-    </row>
-    <row r="305" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="305" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -21744,10 +21173,8 @@
       <c r="AS305" s="1"/>
       <c r="AT305" s="1"/>
       <c r="AU305" s="1"/>
-      <c r="AV305" s="1"/>
-      <c r="AW305" s="1"/>
-    </row>
-    <row r="306" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="306" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -21795,10 +21222,8 @@
       <c r="AS306" s="1"/>
       <c r="AT306" s="1"/>
       <c r="AU306" s="1"/>
-      <c r="AV306" s="1"/>
-      <c r="AW306" s="1"/>
-    </row>
-    <row r="307" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="307" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -21846,10 +21271,8 @@
       <c r="AS307" s="1"/>
       <c r="AT307" s="1"/>
       <c r="AU307" s="1"/>
-      <c r="AV307" s="1"/>
-      <c r="AW307" s="1"/>
-    </row>
-    <row r="308" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="308" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -21897,10 +21320,8 @@
       <c r="AS308" s="1"/>
       <c r="AT308" s="1"/>
       <c r="AU308" s="1"/>
-      <c r="AV308" s="1"/>
-      <c r="AW308" s="1"/>
-    </row>
-    <row r="309" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="309" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -21948,10 +21369,8 @@
       <c r="AS309" s="1"/>
       <c r="AT309" s="1"/>
       <c r="AU309" s="1"/>
-      <c r="AV309" s="1"/>
-      <c r="AW309" s="1"/>
-    </row>
-    <row r="310" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="310" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -21999,10 +21418,8 @@
       <c r="AS310" s="1"/>
       <c r="AT310" s="1"/>
       <c r="AU310" s="1"/>
-      <c r="AV310" s="1"/>
-      <c r="AW310" s="1"/>
-    </row>
-    <row r="311" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="311" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -22050,10 +21467,8 @@
       <c r="AS311" s="1"/>
       <c r="AT311" s="1"/>
       <c r="AU311" s="1"/>
-      <c r="AV311" s="1"/>
-      <c r="AW311" s="1"/>
-    </row>
-    <row r="312" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="312" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -22101,10 +21516,8 @@
       <c r="AS312" s="1"/>
       <c r="AT312" s="1"/>
       <c r="AU312" s="1"/>
-      <c r="AV312" s="1"/>
-      <c r="AW312" s="1"/>
-    </row>
-    <row r="313" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="313" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -22152,10 +21565,8 @@
       <c r="AS313" s="1"/>
       <c r="AT313" s="1"/>
       <c r="AU313" s="1"/>
-      <c r="AV313" s="1"/>
-      <c r="AW313" s="1"/>
-    </row>
-    <row r="314" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="314" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -22203,10 +21614,8 @@
       <c r="AS314" s="1"/>
       <c r="AT314" s="1"/>
       <c r="AU314" s="1"/>
-      <c r="AV314" s="1"/>
-      <c r="AW314" s="1"/>
-    </row>
-    <row r="315" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="315" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -22254,10 +21663,8 @@
       <c r="AS315" s="1"/>
       <c r="AT315" s="1"/>
       <c r="AU315" s="1"/>
-      <c r="AV315" s="1"/>
-      <c r="AW315" s="1"/>
-    </row>
-    <row r="316" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="316" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -22305,10 +21712,8 @@
       <c r="AS316" s="1"/>
       <c r="AT316" s="1"/>
       <c r="AU316" s="1"/>
-      <c r="AV316" s="1"/>
-      <c r="AW316" s="1"/>
-    </row>
-    <row r="317" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="317" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -22356,10 +21761,8 @@
       <c r="AS317" s="1"/>
       <c r="AT317" s="1"/>
       <c r="AU317" s="1"/>
-      <c r="AV317" s="1"/>
-      <c r="AW317" s="1"/>
-    </row>
-    <row r="318" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="318" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -22407,10 +21810,8 @@
       <c r="AS318" s="1"/>
       <c r="AT318" s="1"/>
       <c r="AU318" s="1"/>
-      <c r="AV318" s="1"/>
-      <c r="AW318" s="1"/>
-    </row>
-    <row r="319" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="319" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -22458,10 +21859,8 @@
       <c r="AS319" s="1"/>
       <c r="AT319" s="1"/>
       <c r="AU319" s="1"/>
-      <c r="AV319" s="1"/>
-      <c r="AW319" s="1"/>
-    </row>
-    <row r="320" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="320" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -22509,10 +21908,8 @@
       <c r="AS320" s="1"/>
       <c r="AT320" s="1"/>
       <c r="AU320" s="1"/>
-      <c r="AV320" s="1"/>
-      <c r="AW320" s="1"/>
-    </row>
-    <row r="321" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="321" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -22560,10 +21957,8 @@
       <c r="AS321" s="1"/>
       <c r="AT321" s="1"/>
       <c r="AU321" s="1"/>
-      <c r="AV321" s="1"/>
-      <c r="AW321" s="1"/>
-    </row>
-    <row r="322" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="322" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -22611,10 +22006,8 @@
       <c r="AS322" s="1"/>
       <c r="AT322" s="1"/>
       <c r="AU322" s="1"/>
-      <c r="AV322" s="1"/>
-      <c r="AW322" s="1"/>
-    </row>
-    <row r="323" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="323" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -22662,10 +22055,8 @@
       <c r="AS323" s="1"/>
       <c r="AT323" s="1"/>
       <c r="AU323" s="1"/>
-      <c r="AV323" s="1"/>
-      <c r="AW323" s="1"/>
-    </row>
-    <row r="324" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="324" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -22713,10 +22104,8 @@
       <c r="AS324" s="1"/>
       <c r="AT324" s="1"/>
       <c r="AU324" s="1"/>
-      <c r="AV324" s="1"/>
-      <c r="AW324" s="1"/>
-    </row>
-    <row r="325" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="325" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -22764,10 +22153,8 @@
       <c r="AS325" s="1"/>
       <c r="AT325" s="1"/>
       <c r="AU325" s="1"/>
-      <c r="AV325" s="1"/>
-      <c r="AW325" s="1"/>
-    </row>
-    <row r="326" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="326" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -22815,10 +22202,8 @@
       <c r="AS326" s="1"/>
       <c r="AT326" s="1"/>
       <c r="AU326" s="1"/>
-      <c r="AV326" s="1"/>
-      <c r="AW326" s="1"/>
-    </row>
-    <row r="327" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="327" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -22866,10 +22251,8 @@
       <c r="AS327" s="1"/>
       <c r="AT327" s="1"/>
       <c r="AU327" s="1"/>
-      <c r="AV327" s="1"/>
-      <c r="AW327" s="1"/>
-    </row>
-    <row r="328" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="328" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -22917,10 +22300,8 @@
       <c r="AS328" s="1"/>
       <c r="AT328" s="1"/>
       <c r="AU328" s="1"/>
-      <c r="AV328" s="1"/>
-      <c r="AW328" s="1"/>
-    </row>
-    <row r="329" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="329" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -22968,10 +22349,8 @@
       <c r="AS329" s="1"/>
       <c r="AT329" s="1"/>
       <c r="AU329" s="1"/>
-      <c r="AV329" s="1"/>
-      <c r="AW329" s="1"/>
-    </row>
-    <row r="330" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="330" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -23019,10 +22398,8 @@
       <c r="AS330" s="1"/>
       <c r="AT330" s="1"/>
       <c r="AU330" s="1"/>
-      <c r="AV330" s="1"/>
-      <c r="AW330" s="1"/>
-    </row>
-    <row r="331" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="331" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -23070,10 +22447,8 @@
       <c r="AS331" s="1"/>
       <c r="AT331" s="1"/>
       <c r="AU331" s="1"/>
-      <c r="AV331" s="1"/>
-      <c r="AW331" s="1"/>
-    </row>
-    <row r="332" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="332" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -23121,10 +22496,8 @@
       <c r="AS332" s="1"/>
       <c r="AT332" s="1"/>
       <c r="AU332" s="1"/>
-      <c r="AV332" s="1"/>
-      <c r="AW332" s="1"/>
-    </row>
-    <row r="333" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -23172,10 +22545,8 @@
       <c r="AS333" s="1"/>
       <c r="AT333" s="1"/>
       <c r="AU333" s="1"/>
-      <c r="AV333" s="1"/>
-      <c r="AW333" s="1"/>
-    </row>
-    <row r="334" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="334" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -23223,10 +22594,8 @@
       <c r="AS334" s="1"/>
       <c r="AT334" s="1"/>
       <c r="AU334" s="1"/>
-      <c r="AV334" s="1"/>
-      <c r="AW334" s="1"/>
-    </row>
-    <row r="335" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="335" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -23274,10 +22643,8 @@
       <c r="AS335" s="1"/>
       <c r="AT335" s="1"/>
       <c r="AU335" s="1"/>
-      <c r="AV335" s="1"/>
-      <c r="AW335" s="1"/>
-    </row>
-    <row r="336" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="336" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -23325,10 +22692,8 @@
       <c r="AS336" s="1"/>
       <c r="AT336" s="1"/>
       <c r="AU336" s="1"/>
-      <c r="AV336" s="1"/>
-      <c r="AW336" s="1"/>
-    </row>
-    <row r="337" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="337" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -23376,10 +22741,8 @@
       <c r="AS337" s="1"/>
       <c r="AT337" s="1"/>
       <c r="AU337" s="1"/>
-      <c r="AV337" s="1"/>
-      <c r="AW337" s="1"/>
-    </row>
-    <row r="338" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="338" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -23427,10 +22790,8 @@
       <c r="AS338" s="1"/>
       <c r="AT338" s="1"/>
       <c r="AU338" s="1"/>
-      <c r="AV338" s="1"/>
-      <c r="AW338" s="1"/>
-    </row>
-    <row r="339" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="339" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -23478,10 +22839,8 @@
       <c r="AS339" s="1"/>
       <c r="AT339" s="1"/>
       <c r="AU339" s="1"/>
-      <c r="AV339" s="1"/>
-      <c r="AW339" s="1"/>
-    </row>
-    <row r="340" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="340" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -23529,10 +22888,8 @@
       <c r="AS340" s="1"/>
       <c r="AT340" s="1"/>
       <c r="AU340" s="1"/>
-      <c r="AV340" s="1"/>
-      <c r="AW340" s="1"/>
-    </row>
-    <row r="341" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="341" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -23580,10 +22937,8 @@
       <c r="AS341" s="1"/>
       <c r="AT341" s="1"/>
       <c r="AU341" s="1"/>
-      <c r="AV341" s="1"/>
-      <c r="AW341" s="1"/>
-    </row>
-    <row r="342" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="342" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -23631,10 +22986,8 @@
       <c r="AS342" s="1"/>
       <c r="AT342" s="1"/>
       <c r="AU342" s="1"/>
-      <c r="AV342" s="1"/>
-      <c r="AW342" s="1"/>
-    </row>
-    <row r="343" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="343" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -23682,10 +23035,8 @@
       <c r="AS343" s="1"/>
       <c r="AT343" s="1"/>
       <c r="AU343" s="1"/>
-      <c r="AV343" s="1"/>
-      <c r="AW343" s="1"/>
-    </row>
-    <row r="344" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="344" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -23733,10 +23084,8 @@
       <c r="AS344" s="1"/>
       <c r="AT344" s="1"/>
       <c r="AU344" s="1"/>
-      <c r="AV344" s="1"/>
-      <c r="AW344" s="1"/>
-    </row>
-    <row r="345" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="345" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -23784,10 +23133,8 @@
       <c r="AS345" s="1"/>
       <c r="AT345" s="1"/>
       <c r="AU345" s="1"/>
-      <c r="AV345" s="1"/>
-      <c r="AW345" s="1"/>
-    </row>
-    <row r="346" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="346" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -23835,10 +23182,8 @@
       <c r="AS346" s="1"/>
       <c r="AT346" s="1"/>
       <c r="AU346" s="1"/>
-      <c r="AV346" s="1"/>
-      <c r="AW346" s="1"/>
-    </row>
-    <row r="347" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="347" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -23886,10 +23231,8 @@
       <c r="AS347" s="1"/>
       <c r="AT347" s="1"/>
       <c r="AU347" s="1"/>
-      <c r="AV347" s="1"/>
-      <c r="AW347" s="1"/>
-    </row>
-    <row r="348" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="348" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -23937,10 +23280,8 @@
       <c r="AS348" s="1"/>
       <c r="AT348" s="1"/>
       <c r="AU348" s="1"/>
-      <c r="AV348" s="1"/>
-      <c r="AW348" s="1"/>
-    </row>
-    <row r="349" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="349" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -23988,10 +23329,8 @@
       <c r="AS349" s="1"/>
       <c r="AT349" s="1"/>
       <c r="AU349" s="1"/>
-      <c r="AV349" s="1"/>
-      <c r="AW349" s="1"/>
-    </row>
-    <row r="350" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="350" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -24039,10 +23378,8 @@
       <c r="AS350" s="1"/>
       <c r="AT350" s="1"/>
       <c r="AU350" s="1"/>
-      <c r="AV350" s="1"/>
-      <c r="AW350" s="1"/>
-    </row>
-    <row r="351" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="351" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -24090,10 +23427,8 @@
       <c r="AS351" s="1"/>
       <c r="AT351" s="1"/>
       <c r="AU351" s="1"/>
-      <c r="AV351" s="1"/>
-      <c r="AW351" s="1"/>
-    </row>
-    <row r="352" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="352" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -24141,10 +23476,8 @@
       <c r="AS352" s="1"/>
       <c r="AT352" s="1"/>
       <c r="AU352" s="1"/>
-      <c r="AV352" s="1"/>
-      <c r="AW352" s="1"/>
-    </row>
-    <row r="353" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="353" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -24192,10 +23525,8 @@
       <c r="AS353" s="1"/>
       <c r="AT353" s="1"/>
       <c r="AU353" s="1"/>
-      <c r="AV353" s="1"/>
-      <c r="AW353" s="1"/>
-    </row>
-    <row r="354" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="354" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -24243,10 +23574,8 @@
       <c r="AS354" s="1"/>
       <c r="AT354" s="1"/>
       <c r="AU354" s="1"/>
-      <c r="AV354" s="1"/>
-      <c r="AW354" s="1"/>
-    </row>
-    <row r="355" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="355" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -24294,10 +23623,8 @@
       <c r="AS355" s="1"/>
       <c r="AT355" s="1"/>
       <c r="AU355" s="1"/>
-      <c r="AV355" s="1"/>
-      <c r="AW355" s="1"/>
-    </row>
-    <row r="356" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="356" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -24345,10 +23672,8 @@
       <c r="AS356" s="1"/>
       <c r="AT356" s="1"/>
       <c r="AU356" s="1"/>
-      <c r="AV356" s="1"/>
-      <c r="AW356" s="1"/>
-    </row>
-    <row r="357" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="357" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -24396,10 +23721,8 @@
       <c r="AS357" s="1"/>
       <c r="AT357" s="1"/>
       <c r="AU357" s="1"/>
-      <c r="AV357" s="1"/>
-      <c r="AW357" s="1"/>
-    </row>
-    <row r="358" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="358" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -24447,10 +23770,8 @@
       <c r="AS358" s="1"/>
       <c r="AT358" s="1"/>
       <c r="AU358" s="1"/>
-      <c r="AV358" s="1"/>
-      <c r="AW358" s="1"/>
-    </row>
-    <row r="359" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="359" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -24498,10 +23819,8 @@
       <c r="AS359" s="1"/>
       <c r="AT359" s="1"/>
       <c r="AU359" s="1"/>
-      <c r="AV359" s="1"/>
-      <c r="AW359" s="1"/>
-    </row>
-    <row r="360" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="360" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -24549,10 +23868,8 @@
       <c r="AS360" s="1"/>
       <c r="AT360" s="1"/>
       <c r="AU360" s="1"/>
-      <c r="AV360" s="1"/>
-      <c r="AW360" s="1"/>
-    </row>
-    <row r="361" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="361" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -24600,10 +23917,8 @@
       <c r="AS361" s="1"/>
       <c r="AT361" s="1"/>
       <c r="AU361" s="1"/>
-      <c r="AV361" s="1"/>
-      <c r="AW361" s="1"/>
-    </row>
-    <row r="362" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="362" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -24651,10 +23966,8 @@
       <c r="AS362" s="1"/>
       <c r="AT362" s="1"/>
       <c r="AU362" s="1"/>
-      <c r="AV362" s="1"/>
-      <c r="AW362" s="1"/>
-    </row>
-    <row r="363" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="363" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -24702,10 +24015,8 @@
       <c r="AS363" s="1"/>
       <c r="AT363" s="1"/>
       <c r="AU363" s="1"/>
-      <c r="AV363" s="1"/>
-      <c r="AW363" s="1"/>
-    </row>
-    <row r="364" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="364" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -24753,10 +24064,8 @@
       <c r="AS364" s="1"/>
       <c r="AT364" s="1"/>
       <c r="AU364" s="1"/>
-      <c r="AV364" s="1"/>
-      <c r="AW364" s="1"/>
-    </row>
-    <row r="365" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="365" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -24804,10 +24113,8 @@
       <c r="AS365" s="1"/>
       <c r="AT365" s="1"/>
       <c r="AU365" s="1"/>
-      <c r="AV365" s="1"/>
-      <c r="AW365" s="1"/>
-    </row>
-    <row r="366" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="366" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -24855,10 +24162,8 @@
       <c r="AS366" s="1"/>
       <c r="AT366" s="1"/>
       <c r="AU366" s="1"/>
-      <c r="AV366" s="1"/>
-      <c r="AW366" s="1"/>
-    </row>
-    <row r="367" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="367" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -24906,10 +24211,8 @@
       <c r="AS367" s="1"/>
       <c r="AT367" s="1"/>
       <c r="AU367" s="1"/>
-      <c r="AV367" s="1"/>
-      <c r="AW367" s="1"/>
-    </row>
-    <row r="368" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="368" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -24957,10 +24260,8 @@
       <c r="AS368" s="1"/>
       <c r="AT368" s="1"/>
       <c r="AU368" s="1"/>
-      <c r="AV368" s="1"/>
-      <c r="AW368" s="1"/>
-    </row>
-    <row r="369" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="369" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -25008,10 +24309,8 @@
       <c r="AS369" s="1"/>
       <c r="AT369" s="1"/>
       <c r="AU369" s="1"/>
-      <c r="AV369" s="1"/>
-      <c r="AW369" s="1"/>
-    </row>
-    <row r="370" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="370" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -25059,10 +24358,8 @@
       <c r="AS370" s="1"/>
       <c r="AT370" s="1"/>
       <c r="AU370" s="1"/>
-      <c r="AV370" s="1"/>
-      <c r="AW370" s="1"/>
-    </row>
-    <row r="371" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="371" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -25110,10 +24407,8 @@
       <c r="AS371" s="1"/>
       <c r="AT371" s="1"/>
       <c r="AU371" s="1"/>
-      <c r="AV371" s="1"/>
-      <c r="AW371" s="1"/>
-    </row>
-    <row r="372" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="372" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -25161,10 +24456,8 @@
       <c r="AS372" s="1"/>
       <c r="AT372" s="1"/>
       <c r="AU372" s="1"/>
-      <c r="AV372" s="1"/>
-      <c r="AW372" s="1"/>
-    </row>
-    <row r="373" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="373" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -25212,10 +24505,8 @@
       <c r="AS373" s="1"/>
       <c r="AT373" s="1"/>
       <c r="AU373" s="1"/>
-      <c r="AV373" s="1"/>
-      <c r="AW373" s="1"/>
-    </row>
-    <row r="374" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="374" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -25263,10 +24554,8 @@
       <c r="AS374" s="1"/>
       <c r="AT374" s="1"/>
       <c r="AU374" s="1"/>
-      <c r="AV374" s="1"/>
-      <c r="AW374" s="1"/>
-    </row>
-    <row r="375" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="375" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -25314,10 +24603,8 @@
       <c r="AS375" s="1"/>
       <c r="AT375" s="1"/>
       <c r="AU375" s="1"/>
-      <c r="AV375" s="1"/>
-      <c r="AW375" s="1"/>
-    </row>
-    <row r="376" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="376" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -25365,10 +24652,8 @@
       <c r="AS376" s="1"/>
       <c r="AT376" s="1"/>
       <c r="AU376" s="1"/>
-      <c r="AV376" s="1"/>
-      <c r="AW376" s="1"/>
-    </row>
-    <row r="377" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="377" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -25416,10 +24701,8 @@
       <c r="AS377" s="1"/>
       <c r="AT377" s="1"/>
       <c r="AU377" s="1"/>
-      <c r="AV377" s="1"/>
-      <c r="AW377" s="1"/>
-    </row>
-    <row r="378" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="378" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -25467,10 +24750,8 @@
       <c r="AS378" s="1"/>
       <c r="AT378" s="1"/>
       <c r="AU378" s="1"/>
-      <c r="AV378" s="1"/>
-      <c r="AW378" s="1"/>
-    </row>
-    <row r="379" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="379" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -25518,10 +24799,8 @@
       <c r="AS379" s="1"/>
       <c r="AT379" s="1"/>
       <c r="AU379" s="1"/>
-      <c r="AV379" s="1"/>
-      <c r="AW379" s="1"/>
-    </row>
-    <row r="380" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="380" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -25569,10 +24848,8 @@
       <c r="AS380" s="1"/>
       <c r="AT380" s="1"/>
       <c r="AU380" s="1"/>
-      <c r="AV380" s="1"/>
-      <c r="AW380" s="1"/>
-    </row>
-    <row r="381" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="381" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -25620,10 +24897,8 @@
       <c r="AS381" s="1"/>
       <c r="AT381" s="1"/>
       <c r="AU381" s="1"/>
-      <c r="AV381" s="1"/>
-      <c r="AW381" s="1"/>
-    </row>
-    <row r="382" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="382" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -25671,10 +24946,8 @@
       <c r="AS382" s="1"/>
       <c r="AT382" s="1"/>
       <c r="AU382" s="1"/>
-      <c r="AV382" s="1"/>
-      <c r="AW382" s="1"/>
-    </row>
-    <row r="383" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="383" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -25722,10 +24995,8 @@
       <c r="AS383" s="1"/>
       <c r="AT383" s="1"/>
       <c r="AU383" s="1"/>
-      <c r="AV383" s="1"/>
-      <c r="AW383" s="1"/>
-    </row>
-    <row r="384" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="384" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -25773,10 +25044,8 @@
       <c r="AS384" s="1"/>
       <c r="AT384" s="1"/>
       <c r="AU384" s="1"/>
-      <c r="AV384" s="1"/>
-      <c r="AW384" s="1"/>
-    </row>
-    <row r="385" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="385" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -25824,10 +25093,8 @@
       <c r="AS385" s="1"/>
       <c r="AT385" s="1"/>
       <c r="AU385" s="1"/>
-      <c r="AV385" s="1"/>
-      <c r="AW385" s="1"/>
-    </row>
-    <row r="386" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="386" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -25875,10 +25142,8 @@
       <c r="AS386" s="1"/>
       <c r="AT386" s="1"/>
       <c r="AU386" s="1"/>
-      <c r="AV386" s="1"/>
-      <c r="AW386" s="1"/>
-    </row>
-    <row r="387" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="387" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -25926,10 +25191,8 @@
       <c r="AS387" s="1"/>
       <c r="AT387" s="1"/>
       <c r="AU387" s="1"/>
-      <c r="AV387" s="1"/>
-      <c r="AW387" s="1"/>
-    </row>
-    <row r="388" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="388" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -25977,10 +25240,8 @@
       <c r="AS388" s="1"/>
       <c r="AT388" s="1"/>
       <c r="AU388" s="1"/>
-      <c r="AV388" s="1"/>
-      <c r="AW388" s="1"/>
-    </row>
-    <row r="389" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="389" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -26028,10 +25289,8 @@
       <c r="AS389" s="1"/>
       <c r="AT389" s="1"/>
       <c r="AU389" s="1"/>
-      <c r="AV389" s="1"/>
-      <c r="AW389" s="1"/>
-    </row>
-    <row r="390" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="390" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -26079,10 +25338,8 @@
       <c r="AS390" s="1"/>
       <c r="AT390" s="1"/>
       <c r="AU390" s="1"/>
-      <c r="AV390" s="1"/>
-      <c r="AW390" s="1"/>
-    </row>
-    <row r="391" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="391" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -26130,10 +25387,8 @@
       <c r="AS391" s="1"/>
       <c r="AT391" s="1"/>
       <c r="AU391" s="1"/>
-      <c r="AV391" s="1"/>
-      <c r="AW391" s="1"/>
-    </row>
-    <row r="392" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="392" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -26181,10 +25436,8 @@
       <c r="AS392" s="1"/>
       <c r="AT392" s="1"/>
       <c r="AU392" s="1"/>
-      <c r="AV392" s="1"/>
-      <c r="AW392" s="1"/>
-    </row>
-    <row r="393" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="393" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -26232,10 +25485,8 @@
       <c r="AS393" s="1"/>
       <c r="AT393" s="1"/>
       <c r="AU393" s="1"/>
-      <c r="AV393" s="1"/>
-      <c r="AW393" s="1"/>
-    </row>
-    <row r="394" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="394" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -26283,10 +25534,8 @@
       <c r="AS394" s="1"/>
       <c r="AT394" s="1"/>
       <c r="AU394" s="1"/>
-      <c r="AV394" s="1"/>
-      <c r="AW394" s="1"/>
-    </row>
-    <row r="395" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="395" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -26334,10 +25583,8 @@
       <c r="AS395" s="1"/>
       <c r="AT395" s="1"/>
       <c r="AU395" s="1"/>
-      <c r="AV395" s="1"/>
-      <c r="AW395" s="1"/>
-    </row>
-    <row r="396" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="396" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -26385,10 +25632,8 @@
       <c r="AS396" s="1"/>
       <c r="AT396" s="1"/>
       <c r="AU396" s="1"/>
-      <c r="AV396" s="1"/>
-      <c r="AW396" s="1"/>
-    </row>
-    <row r="397" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="397" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -26436,10 +25681,8 @@
       <c r="AS397" s="1"/>
       <c r="AT397" s="1"/>
       <c r="AU397" s="1"/>
-      <c r="AV397" s="1"/>
-      <c r="AW397" s="1"/>
-    </row>
-    <row r="398" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="398" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -26487,10 +25730,8 @@
       <c r="AS398" s="1"/>
       <c r="AT398" s="1"/>
       <c r="AU398" s="1"/>
-      <c r="AV398" s="1"/>
-      <c r="AW398" s="1"/>
-    </row>
-    <row r="399" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="399" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -26538,10 +25779,8 @@
       <c r="AS399" s="1"/>
       <c r="AT399" s="1"/>
       <c r="AU399" s="1"/>
-      <c r="AV399" s="1"/>
-      <c r="AW399" s="1"/>
-    </row>
-    <row r="400" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="400" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -26589,10 +25828,8 @@
       <c r="AS400" s="1"/>
       <c r="AT400" s="1"/>
       <c r="AU400" s="1"/>
-      <c r="AV400" s="1"/>
-      <c r="AW400" s="1"/>
-    </row>
-    <row r="401" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="401" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -26640,10 +25877,8 @@
       <c r="AS401" s="1"/>
       <c r="AT401" s="1"/>
       <c r="AU401" s="1"/>
-      <c r="AV401" s="1"/>
-      <c r="AW401" s="1"/>
-    </row>
-    <row r="402" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="402" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -26691,10 +25926,8 @@
       <c r="AS402" s="1"/>
       <c r="AT402" s="1"/>
       <c r="AU402" s="1"/>
-      <c r="AV402" s="1"/>
-      <c r="AW402" s="1"/>
-    </row>
-    <row r="403" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="403" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -26742,10 +25975,8 @@
       <c r="AS403" s="1"/>
       <c r="AT403" s="1"/>
       <c r="AU403" s="1"/>
-      <c r="AV403" s="1"/>
-      <c r="AW403" s="1"/>
-    </row>
-    <row r="404" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="404" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -26793,10 +26024,8 @@
       <c r="AS404" s="1"/>
       <c r="AT404" s="1"/>
       <c r="AU404" s="1"/>
-      <c r="AV404" s="1"/>
-      <c r="AW404" s="1"/>
-    </row>
-    <row r="405" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="405" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -26844,10 +26073,8 @@
       <c r="AS405" s="1"/>
       <c r="AT405" s="1"/>
       <c r="AU405" s="1"/>
-      <c r="AV405" s="1"/>
-      <c r="AW405" s="1"/>
-    </row>
-    <row r="406" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="406" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -26895,10 +26122,8 @@
       <c r="AS406" s="1"/>
       <c r="AT406" s="1"/>
       <c r="AU406" s="1"/>
-      <c r="AV406" s="1"/>
-      <c r="AW406" s="1"/>
-    </row>
-    <row r="407" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="407" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -26946,10 +26171,8 @@
       <c r="AS407" s="1"/>
       <c r="AT407" s="1"/>
       <c r="AU407" s="1"/>
-      <c r="AV407" s="1"/>
-      <c r="AW407" s="1"/>
-    </row>
-    <row r="408" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="408" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -26997,10 +26220,8 @@
       <c r="AS408" s="1"/>
       <c r="AT408" s="1"/>
       <c r="AU408" s="1"/>
-      <c r="AV408" s="1"/>
-      <c r="AW408" s="1"/>
-    </row>
-    <row r="409" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="409" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -27048,10 +26269,8 @@
       <c r="AS409" s="1"/>
       <c r="AT409" s="1"/>
       <c r="AU409" s="1"/>
-      <c r="AV409" s="1"/>
-      <c r="AW409" s="1"/>
-    </row>
-    <row r="410" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="410" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -27099,10 +26318,8 @@
       <c r="AS410" s="1"/>
       <c r="AT410" s="1"/>
       <c r="AU410" s="1"/>
-      <c r="AV410" s="1"/>
-      <c r="AW410" s="1"/>
-    </row>
-    <row r="411" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="411" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -27150,10 +26367,8 @@
       <c r="AS411" s="1"/>
       <c r="AT411" s="1"/>
       <c r="AU411" s="1"/>
-      <c r="AV411" s="1"/>
-      <c r="AW411" s="1"/>
-    </row>
-    <row r="412" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="412" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -27201,10 +26416,8 @@
       <c r="AS412" s="1"/>
       <c r="AT412" s="1"/>
       <c r="AU412" s="1"/>
-      <c r="AV412" s="1"/>
-      <c r="AW412" s="1"/>
-    </row>
-    <row r="413" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="413" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -27252,10 +26465,8 @@
       <c r="AS413" s="1"/>
       <c r="AT413" s="1"/>
       <c r="AU413" s="1"/>
-      <c r="AV413" s="1"/>
-      <c r="AW413" s="1"/>
-    </row>
-    <row r="414" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="414" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -27303,10 +26514,8 @@
       <c r="AS414" s="1"/>
       <c r="AT414" s="1"/>
       <c r="AU414" s="1"/>
-      <c r="AV414" s="1"/>
-      <c r="AW414" s="1"/>
-    </row>
-    <row r="415" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="415" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -27354,10 +26563,8 @@
       <c r="AS415" s="1"/>
       <c r="AT415" s="1"/>
       <c r="AU415" s="1"/>
-      <c r="AV415" s="1"/>
-      <c r="AW415" s="1"/>
-    </row>
-    <row r="416" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="416" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -27405,10 +26612,8 @@
       <c r="AS416" s="1"/>
       <c r="AT416" s="1"/>
       <c r="AU416" s="1"/>
-      <c r="AV416" s="1"/>
-      <c r="AW416" s="1"/>
-    </row>
-    <row r="417" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="417" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -27456,10 +26661,8 @@
       <c r="AS417" s="1"/>
       <c r="AT417" s="1"/>
       <c r="AU417" s="1"/>
-      <c r="AV417" s="1"/>
-      <c r="AW417" s="1"/>
-    </row>
-    <row r="418" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="418" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -27507,10 +26710,8 @@
       <c r="AS418" s="1"/>
       <c r="AT418" s="1"/>
       <c r="AU418" s="1"/>
-      <c r="AV418" s="1"/>
-      <c r="AW418" s="1"/>
-    </row>
-    <row r="419" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="419" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -27558,10 +26759,8 @@
       <c r="AS419" s="1"/>
       <c r="AT419" s="1"/>
       <c r="AU419" s="1"/>
-      <c r="AV419" s="1"/>
-      <c r="AW419" s="1"/>
-    </row>
-    <row r="420" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="420" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -27609,10 +26808,8 @@
       <c r="AS420" s="1"/>
       <c r="AT420" s="1"/>
       <c r="AU420" s="1"/>
-      <c r="AV420" s="1"/>
-      <c r="AW420" s="1"/>
-    </row>
-    <row r="421" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="421" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -27660,10 +26857,8 @@
       <c r="AS421" s="1"/>
       <c r="AT421" s="1"/>
       <c r="AU421" s="1"/>
-      <c r="AV421" s="1"/>
-      <c r="AW421" s="1"/>
-    </row>
-    <row r="422" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="422" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -27711,10 +26906,8 @@
       <c r="AS422" s="1"/>
       <c r="AT422" s="1"/>
       <c r="AU422" s="1"/>
-      <c r="AV422" s="1"/>
-      <c r="AW422" s="1"/>
-    </row>
-    <row r="423" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="423" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -27762,10 +26955,8 @@
       <c r="AS423" s="1"/>
       <c r="AT423" s="1"/>
       <c r="AU423" s="1"/>
-      <c r="AV423" s="1"/>
-      <c r="AW423" s="1"/>
-    </row>
-    <row r="424" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="424" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -27813,10 +27004,8 @@
       <c r="AS424" s="1"/>
       <c r="AT424" s="1"/>
       <c r="AU424" s="1"/>
-      <c r="AV424" s="1"/>
-      <c r="AW424" s="1"/>
-    </row>
-    <row r="425" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="425" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -27864,10 +27053,8 @@
       <c r="AS425" s="1"/>
       <c r="AT425" s="1"/>
       <c r="AU425" s="1"/>
-      <c r="AV425" s="1"/>
-      <c r="AW425" s="1"/>
-    </row>
-    <row r="426" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="426" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -27915,10 +27102,8 @@
       <c r="AS426" s="1"/>
       <c r="AT426" s="1"/>
       <c r="AU426" s="1"/>
-      <c r="AV426" s="1"/>
-      <c r="AW426" s="1"/>
-    </row>
-    <row r="427" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="427" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -27966,10 +27151,8 @@
       <c r="AS427" s="1"/>
       <c r="AT427" s="1"/>
       <c r="AU427" s="1"/>
-      <c r="AV427" s="1"/>
-      <c r="AW427" s="1"/>
-    </row>
-    <row r="428" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="428" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -28017,10 +27200,8 @@
       <c r="AS428" s="1"/>
       <c r="AT428" s="1"/>
       <c r="AU428" s="1"/>
-      <c r="AV428" s="1"/>
-      <c r="AW428" s="1"/>
-    </row>
-    <row r="429" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="429" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -28068,10 +27249,8 @@
       <c r="AS429" s="1"/>
       <c r="AT429" s="1"/>
       <c r="AU429" s="1"/>
-      <c r="AV429" s="1"/>
-      <c r="AW429" s="1"/>
-    </row>
-    <row r="430" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="430" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -28119,10 +27298,8 @@
       <c r="AS430" s="1"/>
       <c r="AT430" s="1"/>
       <c r="AU430" s="1"/>
-      <c r="AV430" s="1"/>
-      <c r="AW430" s="1"/>
-    </row>
-    <row r="431" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="431" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -28170,10 +27347,8 @@
       <c r="AS431" s="1"/>
       <c r="AT431" s="1"/>
       <c r="AU431" s="1"/>
-      <c r="AV431" s="1"/>
-      <c r="AW431" s="1"/>
-    </row>
-    <row r="432" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="432" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -28221,10 +27396,8 @@
       <c r="AS432" s="1"/>
       <c r="AT432" s="1"/>
       <c r="AU432" s="1"/>
-      <c r="AV432" s="1"/>
-      <c r="AW432" s="1"/>
-    </row>
-    <row r="433" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="433" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -28272,10 +27445,8 @@
       <c r="AS433" s="1"/>
       <c r="AT433" s="1"/>
       <c r="AU433" s="1"/>
-      <c r="AV433" s="1"/>
-      <c r="AW433" s="1"/>
-    </row>
-    <row r="434" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="434" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -28323,10 +27494,8 @@
       <c r="AS434" s="1"/>
       <c r="AT434" s="1"/>
       <c r="AU434" s="1"/>
-      <c r="AV434" s="1"/>
-      <c r="AW434" s="1"/>
-    </row>
-    <row r="435" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="435" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -28374,10 +27543,8 @@
       <c r="AS435" s="1"/>
       <c r="AT435" s="1"/>
       <c r="AU435" s="1"/>
-      <c r="AV435" s="1"/>
-      <c r="AW435" s="1"/>
-    </row>
-    <row r="436" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="436" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -28425,10 +27592,8 @@
       <c r="AS436" s="1"/>
       <c r="AT436" s="1"/>
       <c r="AU436" s="1"/>
-      <c r="AV436" s="1"/>
-      <c r="AW436" s="1"/>
-    </row>
-    <row r="437" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="437" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -28476,10 +27641,8 @@
       <c r="AS437" s="1"/>
       <c r="AT437" s="1"/>
       <c r="AU437" s="1"/>
-      <c r="AV437" s="1"/>
-      <c r="AW437" s="1"/>
-    </row>
-    <row r="438" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="438" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -28527,10 +27690,8 @@
       <c r="AS438" s="1"/>
       <c r="AT438" s="1"/>
       <c r="AU438" s="1"/>
-      <c r="AV438" s="1"/>
-      <c r="AW438" s="1"/>
-    </row>
-    <row r="439" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="439" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -28578,10 +27739,8 @@
       <c r="AS439" s="1"/>
       <c r="AT439" s="1"/>
       <c r="AU439" s="1"/>
-      <c r="AV439" s="1"/>
-      <c r="AW439" s="1"/>
-    </row>
-    <row r="440" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="440" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -28629,10 +27788,8 @@
       <c r="AS440" s="1"/>
       <c r="AT440" s="1"/>
       <c r="AU440" s="1"/>
-      <c r="AV440" s="1"/>
-      <c r="AW440" s="1"/>
-    </row>
-    <row r="441" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="441" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -28680,10 +27837,8 @@
       <c r="AS441" s="1"/>
       <c r="AT441" s="1"/>
       <c r="AU441" s="1"/>
-      <c r="AV441" s="1"/>
-      <c r="AW441" s="1"/>
-    </row>
-    <row r="442" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="442" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -28731,10 +27886,8 @@
       <c r="AS442" s="1"/>
       <c r="AT442" s="1"/>
       <c r="AU442" s="1"/>
-      <c r="AV442" s="1"/>
-      <c r="AW442" s="1"/>
-    </row>
-    <row r="443" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="443" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -28782,10 +27935,8 @@
       <c r="AS443" s="1"/>
       <c r="AT443" s="1"/>
       <c r="AU443" s="1"/>
-      <c r="AV443" s="1"/>
-      <c r="AW443" s="1"/>
-    </row>
-    <row r="444" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="444" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -28833,10 +27984,8 @@
       <c r="AS444" s="1"/>
       <c r="AT444" s="1"/>
       <c r="AU444" s="1"/>
-      <c r="AV444" s="1"/>
-      <c r="AW444" s="1"/>
-    </row>
-    <row r="445" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="445" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -28884,10 +28033,8 @@
       <c r="AS445" s="1"/>
       <c r="AT445" s="1"/>
       <c r="AU445" s="1"/>
-      <c r="AV445" s="1"/>
-      <c r="AW445" s="1"/>
-    </row>
-    <row r="446" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="446" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -28935,10 +28082,8 @@
       <c r="AS446" s="1"/>
       <c r="AT446" s="1"/>
       <c r="AU446" s="1"/>
-      <c r="AV446" s="1"/>
-      <c r="AW446" s="1"/>
-    </row>
-    <row r="447" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="447" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -28986,10 +28131,8 @@
       <c r="AS447" s="1"/>
       <c r="AT447" s="1"/>
       <c r="AU447" s="1"/>
-      <c r="AV447" s="1"/>
-      <c r="AW447" s="1"/>
-    </row>
-    <row r="448" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="448" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -29037,10 +28180,8 @@
       <c r="AS448" s="1"/>
       <c r="AT448" s="1"/>
       <c r="AU448" s="1"/>
-      <c r="AV448" s="1"/>
-      <c r="AW448" s="1"/>
-    </row>
-    <row r="449" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="449" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -29088,10 +28229,8 @@
       <c r="AS449" s="1"/>
       <c r="AT449" s="1"/>
       <c r="AU449" s="1"/>
-      <c r="AV449" s="1"/>
-      <c r="AW449" s="1"/>
-    </row>
-    <row r="450" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="450" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -29139,10 +28278,8 @@
       <c r="AS450" s="1"/>
       <c r="AT450" s="1"/>
       <c r="AU450" s="1"/>
-      <c r="AV450" s="1"/>
-      <c r="AW450" s="1"/>
-    </row>
-    <row r="451" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="451" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -29190,10 +28327,8 @@
       <c r="AS451" s="1"/>
       <c r="AT451" s="1"/>
       <c r="AU451" s="1"/>
-      <c r="AV451" s="1"/>
-      <c r="AW451" s="1"/>
-    </row>
-    <row r="452" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="452" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -29241,10 +28376,8 @@
       <c r="AS452" s="1"/>
       <c r="AT452" s="1"/>
       <c r="AU452" s="1"/>
-      <c r="AV452" s="1"/>
-      <c r="AW452" s="1"/>
-    </row>
-    <row r="453" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="453" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -29292,10 +28425,8 @@
       <c r="AS453" s="1"/>
       <c r="AT453" s="1"/>
       <c r="AU453" s="1"/>
-      <c r="AV453" s="1"/>
-      <c r="AW453" s="1"/>
-    </row>
-    <row r="454" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="454" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -29343,10 +28474,8 @@
       <c r="AS454" s="1"/>
       <c r="AT454" s="1"/>
       <c r="AU454" s="1"/>
-      <c r="AV454" s="1"/>
-      <c r="AW454" s="1"/>
-    </row>
-    <row r="455" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="455" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -29394,10 +28523,8 @@
       <c r="AS455" s="1"/>
       <c r="AT455" s="1"/>
       <c r="AU455" s="1"/>
-      <c r="AV455" s="1"/>
-      <c r="AW455" s="1"/>
-    </row>
-    <row r="456" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="456" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -29445,10 +28572,8 @@
       <c r="AS456" s="1"/>
       <c r="AT456" s="1"/>
       <c r="AU456" s="1"/>
-      <c r="AV456" s="1"/>
-      <c r="AW456" s="1"/>
-    </row>
-    <row r="457" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="457" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -29496,10 +28621,8 @@
       <c r="AS457" s="1"/>
       <c r="AT457" s="1"/>
       <c r="AU457" s="1"/>
-      <c r="AV457" s="1"/>
-      <c r="AW457" s="1"/>
-    </row>
-    <row r="458" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="458" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -29547,10 +28670,8 @@
       <c r="AS458" s="1"/>
       <c r="AT458" s="1"/>
       <c r="AU458" s="1"/>
-      <c r="AV458" s="1"/>
-      <c r="AW458" s="1"/>
-    </row>
-    <row r="459" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="459" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -29598,10 +28719,8 @@
       <c r="AS459" s="1"/>
       <c r="AT459" s="1"/>
       <c r="AU459" s="1"/>
-      <c r="AV459" s="1"/>
-      <c r="AW459" s="1"/>
-    </row>
-    <row r="460" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="460" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -29649,10 +28768,8 @@
       <c r="AS460" s="1"/>
       <c r="AT460" s="1"/>
       <c r="AU460" s="1"/>
-      <c r="AV460" s="1"/>
-      <c r="AW460" s="1"/>
-    </row>
-    <row r="461" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="461" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -29700,10 +28817,8 @@
       <c r="AS461" s="1"/>
       <c r="AT461" s="1"/>
       <c r="AU461" s="1"/>
-      <c r="AV461" s="1"/>
-      <c r="AW461" s="1"/>
-    </row>
-    <row r="462" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="462" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -29751,10 +28866,8 @@
       <c r="AS462" s="1"/>
       <c r="AT462" s="1"/>
       <c r="AU462" s="1"/>
-      <c r="AV462" s="1"/>
-      <c r="AW462" s="1"/>
-    </row>
-    <row r="463" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="463" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -29802,10 +28915,8 @@
       <c r="AS463" s="1"/>
       <c r="AT463" s="1"/>
       <c r="AU463" s="1"/>
-      <c r="AV463" s="1"/>
-      <c r="AW463" s="1"/>
-    </row>
-    <row r="464" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="464" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -29853,10 +28964,8 @@
       <c r="AS464" s="1"/>
       <c r="AT464" s="1"/>
       <c r="AU464" s="1"/>
-      <c r="AV464" s="1"/>
-      <c r="AW464" s="1"/>
-    </row>
-    <row r="465" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="465" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -29904,10 +29013,8 @@
       <c r="AS465" s="1"/>
       <c r="AT465" s="1"/>
       <c r="AU465" s="1"/>
-      <c r="AV465" s="1"/>
-      <c r="AW465" s="1"/>
-    </row>
-    <row r="466" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="466" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -29955,10 +29062,8 @@
       <c r="AS466" s="1"/>
       <c r="AT466" s="1"/>
       <c r="AU466" s="1"/>
-      <c r="AV466" s="1"/>
-      <c r="AW466" s="1"/>
-    </row>
-    <row r="467" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="467" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -30006,10 +29111,8 @@
       <c r="AS467" s="1"/>
       <c r="AT467" s="1"/>
       <c r="AU467" s="1"/>
-      <c r="AV467" s="1"/>
-      <c r="AW467" s="1"/>
-    </row>
-    <row r="468" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="468" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -30057,10 +29160,8 @@
       <c r="AS468" s="1"/>
       <c r="AT468" s="1"/>
       <c r="AU468" s="1"/>
-      <c r="AV468" s="1"/>
-      <c r="AW468" s="1"/>
-    </row>
-    <row r="469" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="469" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -30108,10 +29209,8 @@
       <c r="AS469" s="1"/>
       <c r="AT469" s="1"/>
       <c r="AU469" s="1"/>
-      <c r="AV469" s="1"/>
-      <c r="AW469" s="1"/>
-    </row>
-    <row r="470" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="470" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -30159,10 +29258,8 @@
       <c r="AS470" s="1"/>
       <c r="AT470" s="1"/>
       <c r="AU470" s="1"/>
-      <c r="AV470" s="1"/>
-      <c r="AW470" s="1"/>
-    </row>
-    <row r="471" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="471" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -30210,10 +29307,8 @@
       <c r="AS471" s="1"/>
       <c r="AT471" s="1"/>
       <c r="AU471" s="1"/>
-      <c r="AV471" s="1"/>
-      <c r="AW471" s="1"/>
-    </row>
-    <row r="472" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="472" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -30261,10 +29356,8 @@
       <c r="AS472" s="1"/>
       <c r="AT472" s="1"/>
       <c r="AU472" s="1"/>
-      <c r="AV472" s="1"/>
-      <c r="AW472" s="1"/>
-    </row>
-    <row r="473" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="473" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -30312,10 +29405,8 @@
       <c r="AS473" s="1"/>
       <c r="AT473" s="1"/>
       <c r="AU473" s="1"/>
-      <c r="AV473" s="1"/>
-      <c r="AW473" s="1"/>
-    </row>
-    <row r="474" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="474" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -30363,10 +29454,8 @@
       <c r="AS474" s="1"/>
       <c r="AT474" s="1"/>
       <c r="AU474" s="1"/>
-      <c r="AV474" s="1"/>
-      <c r="AW474" s="1"/>
-    </row>
-    <row r="475" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="475" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -30414,10 +29503,8 @@
       <c r="AS475" s="1"/>
       <c r="AT475" s="1"/>
       <c r="AU475" s="1"/>
-      <c r="AV475" s="1"/>
-      <c r="AW475" s="1"/>
-    </row>
-    <row r="476" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="476" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -30465,10 +29552,8 @@
       <c r="AS476" s="1"/>
       <c r="AT476" s="1"/>
       <c r="AU476" s="1"/>
-      <c r="AV476" s="1"/>
-      <c r="AW476" s="1"/>
-    </row>
-    <row r="477" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="477" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -30516,10 +29601,8 @@
       <c r="AS477" s="1"/>
       <c r="AT477" s="1"/>
       <c r="AU477" s="1"/>
-      <c r="AV477" s="1"/>
-      <c r="AW477" s="1"/>
-    </row>
-    <row r="478" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="478" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -30567,10 +29650,8 @@
       <c r="AS478" s="1"/>
       <c r="AT478" s="1"/>
       <c r="AU478" s="1"/>
-      <c r="AV478" s="1"/>
-      <c r="AW478" s="1"/>
-    </row>
-    <row r="479" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="479" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -30618,10 +29699,8 @@
       <c r="AS479" s="1"/>
       <c r="AT479" s="1"/>
       <c r="AU479" s="1"/>
-      <c r="AV479" s="1"/>
-      <c r="AW479" s="1"/>
-    </row>
-    <row r="480" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="480" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -30669,10 +29748,8 @@
       <c r="AS480" s="1"/>
       <c r="AT480" s="1"/>
       <c r="AU480" s="1"/>
-      <c r="AV480" s="1"/>
-      <c r="AW480" s="1"/>
-    </row>
-    <row r="481" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="481" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -30720,10 +29797,8 @@
       <c r="AS481" s="1"/>
       <c r="AT481" s="1"/>
       <c r="AU481" s="1"/>
-      <c r="AV481" s="1"/>
-      <c r="AW481" s="1"/>
-    </row>
-    <row r="482" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="482" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -30771,10 +29846,8 @@
       <c r="AS482" s="1"/>
       <c r="AT482" s="1"/>
       <c r="AU482" s="1"/>
-      <c r="AV482" s="1"/>
-      <c r="AW482" s="1"/>
-    </row>
-    <row r="483" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="483" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -30822,10 +29895,8 @@
       <c r="AS483" s="1"/>
       <c r="AT483" s="1"/>
       <c r="AU483" s="1"/>
-      <c r="AV483" s="1"/>
-      <c r="AW483" s="1"/>
-    </row>
-    <row r="484" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="484" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -30873,10 +29944,8 @@
       <c r="AS484" s="1"/>
       <c r="AT484" s="1"/>
       <c r="AU484" s="1"/>
-      <c r="AV484" s="1"/>
-      <c r="AW484" s="1"/>
-    </row>
-    <row r="485" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="485" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -30924,10 +29993,8 @@
       <c r="AS485" s="1"/>
       <c r="AT485" s="1"/>
       <c r="AU485" s="1"/>
-      <c r="AV485" s="1"/>
-      <c r="AW485" s="1"/>
-    </row>
-    <row r="486" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="486" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -30975,10 +30042,8 @@
       <c r="AS486" s="1"/>
       <c r="AT486" s="1"/>
       <c r="AU486" s="1"/>
-      <c r="AV486" s="1"/>
-      <c r="AW486" s="1"/>
-    </row>
-    <row r="487" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="487" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -31026,10 +30091,8 @@
       <c r="AS487" s="1"/>
       <c r="AT487" s="1"/>
       <c r="AU487" s="1"/>
-      <c r="AV487" s="1"/>
-      <c r="AW487" s="1"/>
-    </row>
-    <row r="488" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="488" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -31077,10 +30140,8 @@
       <c r="AS488" s="1"/>
       <c r="AT488" s="1"/>
       <c r="AU488" s="1"/>
-      <c r="AV488" s="1"/>
-      <c r="AW488" s="1"/>
-    </row>
-    <row r="489" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="489" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -31128,10 +30189,8 @@
       <c r="AS489" s="1"/>
       <c r="AT489" s="1"/>
       <c r="AU489" s="1"/>
-      <c r="AV489" s="1"/>
-      <c r="AW489" s="1"/>
-    </row>
-    <row r="490" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="490" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -31179,10 +30238,8 @@
       <c r="AS490" s="1"/>
       <c r="AT490" s="1"/>
       <c r="AU490" s="1"/>
-      <c r="AV490" s="1"/>
-      <c r="AW490" s="1"/>
-    </row>
-    <row r="491" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="491" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -31230,10 +30287,8 @@
       <c r="AS491" s="1"/>
       <c r="AT491" s="1"/>
       <c r="AU491" s="1"/>
-      <c r="AV491" s="1"/>
-      <c r="AW491" s="1"/>
-    </row>
-    <row r="492" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="492" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -31281,10 +30336,8 @@
       <c r="AS492" s="1"/>
       <c r="AT492" s="1"/>
       <c r="AU492" s="1"/>
-      <c r="AV492" s="1"/>
-      <c r="AW492" s="1"/>
-    </row>
-    <row r="493" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="493" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -31332,10 +30385,8 @@
       <c r="AS493" s="1"/>
       <c r="AT493" s="1"/>
       <c r="AU493" s="1"/>
-      <c r="AV493" s="1"/>
-      <c r="AW493" s="1"/>
-    </row>
-    <row r="494" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="494" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -31383,10 +30434,8 @@
       <c r="AS494" s="1"/>
       <c r="AT494" s="1"/>
       <c r="AU494" s="1"/>
-      <c r="AV494" s="1"/>
-      <c r="AW494" s="1"/>
-    </row>
-    <row r="495" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="495" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -31434,10 +30483,8 @@
       <c r="AS495" s="1"/>
       <c r="AT495" s="1"/>
       <c r="AU495" s="1"/>
-      <c r="AV495" s="1"/>
-      <c r="AW495" s="1"/>
-    </row>
-    <row r="496" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="496" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -31485,10 +30532,8 @@
       <c r="AS496" s="1"/>
       <c r="AT496" s="1"/>
       <c r="AU496" s="1"/>
-      <c r="AV496" s="1"/>
-      <c r="AW496" s="1"/>
-    </row>
-    <row r="497" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="497" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -31536,10 +30581,8 @@
       <c r="AS497" s="1"/>
       <c r="AT497" s="1"/>
       <c r="AU497" s="1"/>
-      <c r="AV497" s="1"/>
-      <c r="AW497" s="1"/>
-    </row>
-    <row r="498" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="498" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -31587,10 +30630,8 @@
       <c r="AS498" s="1"/>
       <c r="AT498" s="1"/>
       <c r="AU498" s="1"/>
-      <c r="AV498" s="1"/>
-      <c r="AW498" s="1"/>
-    </row>
-    <row r="499" spans="1:49" x14ac:dyDescent="0.25">
+    </row>
+    <row r="499" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -31638,33 +30679,9 @@
       <c r="AS499" s="1"/>
       <c r="AT499" s="1"/>
       <c r="AU499" s="1"/>
-      <c r="AV499" s="1"/>
-      <c r="AW499" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AC104" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <filters blank="1">
-        <filter val="0,09"/>
-        <filter val="0,10"/>
-        <filter val="0,12"/>
-        <filter val="0,14"/>
-        <filter val="0,15"/>
-        <filter val="0,18"/>
-        <filter val="0,22"/>
-        <filter val="0,25"/>
-        <filter val="0,28"/>
-        <filter val="0,30"/>
-        <filter val="0,33"/>
-        <filter val="0,35"/>
-        <filter val="0,36"/>
-        <filter val="0,40"/>
-        <filter val="0,41"/>
-        <filter val="0,84"/>
-        <filter val="1,00"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:AC104" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
